--- a/backend/database/seeders/EscuelasVC.xlsx
+++ b/backend/database/seeders/EscuelasVC.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\bebrascubarui\api\database\seeders\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\bebrascuba\api\database\seeders\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CBDEE13-65B6-4DE4-BC6A-2AB4D8C4E33E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{056E0707-4005-4930-B70E-C25F2629D2A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{5606E16E-E496-426F-8F21-53D678AA02FC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5606E16E-E496-426F-8F21-53D678AA02FC}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$E$559</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -1854,9 +1854,6 @@
     <t>26090405</t>
   </si>
   <si>
-    <t>Olga Alonso gonzález</t>
-  </si>
-  <si>
     <t>26090340</t>
   </si>
   <si>
@@ -3646,24 +3643,28 @@
   </si>
   <si>
     <t>Sagua la Grande</t>
+  </si>
+  <si>
+    <t>Olga Alonso González</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -3686,14 +3687,21 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -4238,15 +4246,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D186CE86-78E5-400A-95E9-7078AC52DD14}">
   <dimension ref="A1:E559"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" customWidth="1"/>
-    <col min="2" max="2" width="34.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.625" customWidth="1"/>
+    <col min="2" max="2" width="34.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.375" customWidth="1"/>
+    <col min="5" max="5" width="20.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4260,10 +4268,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>1199</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -4280,7 +4288,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -4297,7 +4305,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -4314,7 +4322,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -4331,7 +4339,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -4348,7 +4356,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
@@ -4365,7 +4373,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
@@ -4382,7 +4390,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
@@ -4399,7 +4407,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
@@ -4416,7 +4424,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>4</v>
       </c>
@@ -4433,7 +4441,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>4</v>
       </c>
@@ -4450,7 +4458,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>4</v>
       </c>
@@ -4467,7 +4475,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>4</v>
       </c>
@@ -4484,7 +4492,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>4</v>
       </c>
@@ -4501,7 +4509,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>4</v>
       </c>
@@ -4518,7 +4526,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>4</v>
       </c>
@@ -4535,7 +4543,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>4</v>
       </c>
@@ -4552,7 +4560,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>4</v>
       </c>
@@ -4569,7 +4577,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>4</v>
       </c>
@@ -4586,7 +4594,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>4</v>
       </c>
@@ -4603,7 +4611,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>4</v>
       </c>
@@ -4620,7 +4628,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>4</v>
       </c>
@@ -4637,7 +4645,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>4</v>
       </c>
@@ -4654,7 +4662,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>4</v>
       </c>
@@ -4668,12 +4676,12 @@
         <v>7</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>75</v>
@@ -4688,9 +4696,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>5</v>
@@ -4705,9 +4713,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>80</v>
@@ -4722,9 +4730,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>82</v>
@@ -4739,9 +4747,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>85</v>
@@ -4756,9 +4764,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B31" s="8" t="s">
         <v>88</v>
@@ -4773,9 +4781,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B32" s="8" t="s">
         <v>52</v>
@@ -4790,9 +4798,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B33" s="8" t="s">
         <v>93</v>
@@ -4807,9 +4815,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B34" s="8" t="s">
         <v>96</v>
@@ -4824,9 +4832,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B35" s="8" t="s">
         <v>99</v>
@@ -4841,9 +4849,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B36" s="8" t="s">
         <v>102</v>
@@ -4858,9 +4866,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B37" s="8" t="s">
         <v>105</v>
@@ -4875,9 +4883,9 @@
         <v>108</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>109</v>
@@ -4892,9 +4900,9 @@
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B39" s="8" t="s">
         <v>111</v>
@@ -4909,9 +4917,9 @@
         <v>66</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B40" s="8" t="s">
         <v>113</v>
@@ -4926,9 +4934,9 @@
         <v>66</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B41" s="8" t="s">
         <v>115</v>
@@ -4943,9 +4951,9 @@
         <v>66</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B42" s="8" t="s">
         <v>117</v>
@@ -4960,9 +4968,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B43" s="8" t="s">
         <v>115</v>
@@ -4977,9 +4985,9 @@
         <v>120</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B44" s="8" t="s">
         <v>121</v>
@@ -4991,12 +4999,12 @@
         <v>77</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B45" s="8" t="s">
         <v>123</v>
@@ -5011,9 +5019,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>125</v>
@@ -5028,9 +5036,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>127</v>
@@ -5045,9 +5053,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>129</v>
@@ -5062,9 +5070,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B49" s="8" t="s">
         <v>131</v>
@@ -5079,9 +5087,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>132</v>
@@ -5096,9 +5104,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>133</v>
@@ -5113,9 +5121,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>135</v>
@@ -5130,9 +5138,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>136</v>
@@ -5147,9 +5155,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>137</v>
@@ -5164,9 +5172,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>138</v>
@@ -5181,9 +5189,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>139</v>
@@ -5198,9 +5206,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>140</v>
@@ -5215,9 +5223,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>141</v>
@@ -5232,9 +5240,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>142</v>
@@ -5249,9 +5257,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>144</v>
@@ -5266,9 +5274,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>146</v>
@@ -5283,9 +5291,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>147</v>
@@ -5300,9 +5308,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>149</v>
@@ -5317,9 +5325,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>151</v>
@@ -5334,9 +5342,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>152</v>
@@ -5351,9 +5359,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>154</v>
@@ -5368,9 +5376,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>156</v>
@@ -5385,9 +5393,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>158</v>
@@ -5402,9 +5410,9 @@
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>159</v>
@@ -5419,9 +5427,9 @@
         <v>66</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B70" s="7" t="s">
         <v>160</v>
@@ -5436,9 +5444,9 @@
         <v>161</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>162</v>
@@ -5453,9 +5461,9 @@
         <v>66</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>163</v>
@@ -5470,9 +5478,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>164</v>
@@ -5484,12 +5492,12 @@
         <v>130</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>165</v>
@@ -5504,9 +5512,9 @@
         <v>120</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>166</v>
@@ -5521,9 +5529,9 @@
         <v>120</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>159</v>
@@ -5538,7 +5546,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
         <v>168</v>
       </c>
@@ -5555,7 +5563,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
         <v>168</v>
       </c>
@@ -5572,7 +5580,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
         <v>168</v>
       </c>
@@ -5589,7 +5597,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
         <v>168</v>
       </c>
@@ -5606,7 +5614,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
         <v>168</v>
       </c>
@@ -5623,7 +5631,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>168</v>
       </c>
@@ -5640,7 +5648,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
         <v>168</v>
       </c>
@@ -5657,7 +5665,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
         <v>168</v>
       </c>
@@ -5674,7 +5682,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
         <v>168</v>
       </c>
@@ -5691,7 +5699,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
         <v>168</v>
       </c>
@@ -5708,7 +5716,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
         <v>168</v>
       </c>
@@ -5725,7 +5733,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
         <v>168</v>
       </c>
@@ -5740,7 +5748,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
         <v>168</v>
       </c>
@@ -5757,7 +5765,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
         <v>168</v>
       </c>
@@ -5774,7 +5782,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
         <v>168</v>
       </c>
@@ -5791,7 +5799,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
         <v>168</v>
       </c>
@@ -5808,7 +5816,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
         <v>168</v>
       </c>
@@ -5825,7 +5833,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
         <v>168</v>
       </c>
@@ -5842,7 +5850,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
         <v>168</v>
       </c>
@@ -5859,7 +5867,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
         <v>168</v>
       </c>
@@ -5876,7 +5884,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
         <v>168</v>
       </c>
@@ -5893,7 +5901,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
         <v>168</v>
       </c>
@@ -5910,7 +5918,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
         <v>168</v>
       </c>
@@ -5927,7 +5935,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
         <v>168</v>
       </c>
@@ -5944,7 +5952,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
         <v>168</v>
       </c>
@@ -5961,7 +5969,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
         <v>168</v>
       </c>
@@ -5978,7 +5986,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
         <v>168</v>
       </c>
@@ -5995,7 +6003,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
         <v>168</v>
       </c>
@@ -6012,7 +6020,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
         <v>168</v>
       </c>
@@ -6029,7 +6037,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
         <v>168</v>
       </c>
@@ -6046,7 +6054,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
         <v>168</v>
       </c>
@@ -6063,7 +6071,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
         <v>168</v>
       </c>
@@ -6080,7 +6088,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
         <v>168</v>
       </c>
@@ -6094,10 +6102,10 @@
         <v>179</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
         <v>168</v>
       </c>
@@ -6114,7 +6122,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
         <v>255</v>
       </c>
@@ -6131,7 +6139,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
         <v>255</v>
       </c>
@@ -6148,7 +6156,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
         <v>255</v>
       </c>
@@ -6165,7 +6173,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
         <v>255</v>
       </c>
@@ -6182,7 +6190,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
         <v>255</v>
       </c>
@@ -6199,7 +6207,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
         <v>255</v>
       </c>
@@ -6216,7 +6224,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
         <v>255</v>
       </c>
@@ -6233,7 +6241,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
         <v>255</v>
       </c>
@@ -6250,7 +6258,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
         <v>255</v>
       </c>
@@ -6267,7 +6275,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
         <v>255</v>
       </c>
@@ -6284,7 +6292,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
         <v>255</v>
       </c>
@@ -6301,7 +6309,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
         <v>255</v>
       </c>
@@ -6318,7 +6326,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
         <v>255</v>
       </c>
@@ -6335,7 +6343,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
         <v>255</v>
       </c>
@@ -6352,7 +6360,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
         <v>255</v>
       </c>
@@ -6369,7 +6377,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
         <v>255</v>
       </c>
@@ -6386,7 +6394,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
         <v>255</v>
       </c>
@@ -6403,7 +6411,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
         <v>255</v>
       </c>
@@ -6420,7 +6428,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
         <v>255</v>
       </c>
@@ -6437,7 +6445,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
         <v>255</v>
       </c>
@@ -6454,7 +6462,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
         <v>255</v>
       </c>
@@ -6471,7 +6479,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
         <v>255</v>
       </c>
@@ -6488,7 +6496,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" s="2" t="s">
         <v>255</v>
       </c>
@@ -6505,7 +6513,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
         <v>255</v>
       </c>
@@ -6522,7 +6530,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
         <v>255</v>
       </c>
@@ -6539,7 +6547,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
         <v>255</v>
       </c>
@@ -6556,7 +6564,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
         <v>255</v>
       </c>
@@ -6571,7 +6579,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
         <v>255</v>
       </c>
@@ -6588,7 +6596,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
         <v>255</v>
       </c>
@@ -6605,7 +6613,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
         <v>255</v>
       </c>
@@ -6622,7 +6630,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
         <v>255</v>
       </c>
@@ -6639,7 +6647,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
         <v>255</v>
       </c>
@@ -6656,7 +6664,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A143" s="2" t="s">
         <v>255</v>
       </c>
@@ -6673,7 +6681,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" s="2" t="s">
         <v>255</v>
       </c>
@@ -6690,7 +6698,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
         <v>255</v>
       </c>
@@ -6707,7 +6715,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
         <v>255</v>
       </c>
@@ -6724,7 +6732,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
         <v>255</v>
       </c>
@@ -6741,7 +6749,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148" s="2" t="s">
         <v>255</v>
       </c>
@@ -6758,7 +6766,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A149" s="2" t="s">
         <v>255</v>
       </c>
@@ -6775,7 +6783,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
         <v>255</v>
       </c>
@@ -6792,7 +6800,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
         <v>255</v>
       </c>
@@ -6809,7 +6817,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
         <v>255</v>
       </c>
@@ -6826,7 +6834,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A153" s="2" t="s">
         <v>255</v>
       </c>
@@ -6843,7 +6851,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154" s="2" t="s">
         <v>255</v>
       </c>
@@ -6860,7 +6868,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A155" s="2" t="s">
         <v>255</v>
       </c>
@@ -6877,7 +6885,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A156" s="2" t="s">
         <v>255</v>
       </c>
@@ -6894,7 +6902,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" s="2" t="s">
         <v>255</v>
       </c>
@@ -6911,7 +6919,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" s="2" t="s">
         <v>255</v>
       </c>
@@ -6925,10 +6933,10 @@
         <v>255</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" s="2" t="s">
         <v>255</v>
       </c>
@@ -6945,7 +6953,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" s="2" t="s">
         <v>255</v>
       </c>
@@ -6962,7 +6970,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A161" s="2" t="s">
         <v>255</v>
       </c>
@@ -6979,7 +6987,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A162" s="2" t="s">
         <v>367</v>
       </c>
@@ -6996,7 +7004,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A163" s="2" t="s">
         <v>367</v>
       </c>
@@ -7013,7 +7021,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A164" s="2" t="s">
         <v>367</v>
       </c>
@@ -7030,7 +7038,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A165" s="2" t="s">
         <v>367</v>
       </c>
@@ -7047,7 +7055,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A166" s="2" t="s">
         <v>367</v>
       </c>
@@ -7064,7 +7072,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A167" s="2" t="s">
         <v>367</v>
       </c>
@@ -7081,7 +7089,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A168" s="2" t="s">
         <v>367</v>
       </c>
@@ -7098,7 +7106,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A169" s="2" t="s">
         <v>367</v>
       </c>
@@ -7115,7 +7123,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A170" s="2" t="s">
         <v>367</v>
       </c>
@@ -7132,7 +7140,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A171" s="2" t="s">
         <v>367</v>
       </c>
@@ -7149,7 +7157,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A172" s="2" t="s">
         <v>367</v>
       </c>
@@ -7166,7 +7174,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A173" s="2" t="s">
         <v>367</v>
       </c>
@@ -7183,7 +7191,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A174" s="2" t="s">
         <v>367</v>
       </c>
@@ -7200,7 +7208,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A175" s="2" t="s">
         <v>367</v>
       </c>
@@ -7217,7 +7225,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A176" s="2" t="s">
         <v>367</v>
       </c>
@@ -7234,7 +7242,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A177" s="2" t="s">
         <v>367</v>
       </c>
@@ -7251,7 +7259,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A178" s="2" t="s">
         <v>367</v>
       </c>
@@ -7268,7 +7276,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A179" s="2" t="s">
         <v>367</v>
       </c>
@@ -7285,7 +7293,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A180" s="2" t="s">
         <v>367</v>
       </c>
@@ -7299,10 +7307,10 @@
         <v>367</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A181" s="2" t="s">
         <v>367</v>
       </c>
@@ -7319,7 +7327,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A182" s="2" t="s">
         <v>367</v>
       </c>
@@ -7336,7 +7344,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A183" s="2" t="s">
         <v>405</v>
       </c>
@@ -7353,7 +7361,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A184" s="2" t="s">
         <v>405</v>
       </c>
@@ -7370,7 +7378,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A185" s="2" t="s">
         <v>405</v>
       </c>
@@ -7387,7 +7395,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A186" s="2" t="s">
         <v>405</v>
       </c>
@@ -7404,7 +7412,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A187" s="2" t="s">
         <v>405</v>
       </c>
@@ -7421,7 +7429,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A188" s="2" t="s">
         <v>405</v>
       </c>
@@ -7438,7 +7446,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A189" s="2" t="s">
         <v>405</v>
       </c>
@@ -7455,7 +7463,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A190" s="2" t="s">
         <v>405</v>
       </c>
@@ -7472,7 +7480,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A191" s="2" t="s">
         <v>405</v>
       </c>
@@ -7489,7 +7497,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A192" s="2" t="s">
         <v>405</v>
       </c>
@@ -7506,7 +7514,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A193" s="2" t="s">
         <v>405</v>
       </c>
@@ -7523,7 +7531,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A194" s="2" t="s">
         <v>405</v>
       </c>
@@ -7540,7 +7548,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A195" s="2" t="s">
         <v>405</v>
       </c>
@@ -7557,7 +7565,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A196" s="2" t="s">
         <v>405</v>
       </c>
@@ -7574,7 +7582,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A197" s="2" t="s">
         <v>405</v>
       </c>
@@ -7591,7 +7599,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A198" s="2" t="s">
         <v>405</v>
       </c>
@@ -7608,7 +7616,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A199" s="2" t="s">
         <v>405</v>
       </c>
@@ -7625,7 +7633,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A200" s="2" t="s">
         <v>405</v>
       </c>
@@ -7642,7 +7650,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A201" s="2" t="s">
         <v>405</v>
       </c>
@@ -7659,7 +7667,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A202" s="2" t="s">
         <v>405</v>
       </c>
@@ -7676,7 +7684,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A203" s="2" t="s">
         <v>405</v>
       </c>
@@ -7693,7 +7701,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A204" s="2" t="s">
         <v>405</v>
       </c>
@@ -7710,7 +7718,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A205" s="2" t="s">
         <v>405</v>
       </c>
@@ -7727,7 +7735,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A206" s="2" t="s">
         <v>405</v>
       </c>
@@ -7744,7 +7752,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A207" s="2" t="s">
         <v>405</v>
       </c>
@@ -7761,7 +7769,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A208" s="2" t="s">
         <v>405</v>
       </c>
@@ -7778,7 +7786,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A209" s="2" t="s">
         <v>405</v>
       </c>
@@ -7795,7 +7803,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A210" s="2" t="s">
         <v>405</v>
       </c>
@@ -7812,7 +7820,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A211" s="2" t="s">
         <v>405</v>
       </c>
@@ -7829,7 +7837,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A212" s="2" t="s">
         <v>405</v>
       </c>
@@ -7846,7 +7854,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A213" s="2" t="s">
         <v>405</v>
       </c>
@@ -7863,7 +7871,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A214" s="2" t="s">
         <v>405</v>
       </c>
@@ -7880,7 +7888,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A215" s="2" t="s">
         <v>405</v>
       </c>
@@ -7897,7 +7905,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A216" s="2" t="s">
         <v>405</v>
       </c>
@@ -7914,7 +7922,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A217" s="2" t="s">
         <v>405</v>
       </c>
@@ -7931,7 +7939,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A218" s="2" t="s">
         <v>405</v>
       </c>
@@ -7945,10 +7953,10 @@
         <v>408</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A219" s="2" t="s">
         <v>405</v>
       </c>
@@ -7965,7 +7973,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A220" s="2" t="s">
         <v>405</v>
       </c>
@@ -7982,7 +7990,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A221" s="2" t="s">
         <v>491</v>
       </c>
@@ -7999,7 +8007,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A222" s="2" t="s">
         <v>491</v>
       </c>
@@ -8016,7 +8024,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A223" s="2" t="s">
         <v>491</v>
       </c>
@@ -8033,7 +8041,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A224" s="2" t="s">
         <v>491</v>
       </c>
@@ -8050,7 +8058,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A225" s="2" t="s">
         <v>491</v>
       </c>
@@ -8067,7 +8075,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A226" s="2" t="s">
         <v>491</v>
       </c>
@@ -8084,7 +8092,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A227" s="2" t="s">
         <v>491</v>
       </c>
@@ -8101,7 +8109,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A228" s="2" t="s">
         <v>491</v>
       </c>
@@ -8118,7 +8126,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A229" s="2" t="s">
         <v>491</v>
       </c>
@@ -8135,7 +8143,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A230" s="2" t="s">
         <v>491</v>
       </c>
@@ -8152,7 +8160,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A231" s="2" t="s">
         <v>491</v>
       </c>
@@ -8169,7 +8177,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A232" s="2" t="s">
         <v>491</v>
       </c>
@@ -8186,7 +8194,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A233" s="2" t="s">
         <v>491</v>
       </c>
@@ -8203,7 +8211,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A234" s="2" t="s">
         <v>491</v>
       </c>
@@ -8220,7 +8228,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A235" s="2" t="s">
         <v>491</v>
       </c>
@@ -8237,7 +8245,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A236" s="2" t="s">
         <v>491</v>
       </c>
@@ -8254,7 +8262,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A237" s="2" t="s">
         <v>491</v>
       </c>
@@ -8271,7 +8279,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A238" s="2" t="s">
         <v>491</v>
       </c>
@@ -8288,7 +8296,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A239" s="2" t="s">
         <v>491</v>
       </c>
@@ -8305,7 +8313,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A240" s="2" t="s">
         <v>491</v>
       </c>
@@ -8322,7 +8330,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A241" s="2" t="s">
         <v>491</v>
       </c>
@@ -8339,7 +8347,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A242" s="2" t="s">
         <v>491</v>
       </c>
@@ -8356,7 +8364,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A243" s="2" t="s">
         <v>491</v>
       </c>
@@ -8371,7 +8379,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A244" s="2" t="s">
         <v>491</v>
       </c>
@@ -8388,7 +8396,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A245" s="2" t="s">
         <v>491</v>
       </c>
@@ -8405,7 +8413,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A246" s="2" t="s">
         <v>491</v>
       </c>
@@ -8422,7 +8430,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A247" s="2" t="s">
         <v>491</v>
       </c>
@@ -8439,7 +8447,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A248" s="2" t="s">
         <v>491</v>
       </c>
@@ -8456,7 +8464,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A249" s="2" t="s">
         <v>491</v>
       </c>
@@ -8473,7 +8481,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A250" s="2" t="s">
         <v>491</v>
       </c>
@@ -8490,7 +8498,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A251" s="2" t="s">
         <v>491</v>
       </c>
@@ -8507,7 +8515,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A252" s="2" t="s">
         <v>491</v>
       </c>
@@ -8524,7 +8532,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A253" s="2" t="s">
         <v>491</v>
       </c>
@@ -8539,7 +8547,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A254" s="2" t="s">
         <v>491</v>
       </c>
@@ -8556,7 +8564,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A255" s="2" t="s">
         <v>491</v>
       </c>
@@ -8573,7 +8581,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A256" s="2" t="s">
         <v>491</v>
       </c>
@@ -8590,7 +8598,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A257" s="2" t="s">
         <v>491</v>
       </c>
@@ -8607,7 +8615,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A258" s="2" t="s">
         <v>491</v>
       </c>
@@ -8622,7 +8630,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A259" s="2" t="s">
         <v>491</v>
       </c>
@@ -8637,7 +8645,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A260" s="2" t="s">
         <v>491</v>
       </c>
@@ -8654,7 +8662,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A261" s="2" t="s">
         <v>491</v>
       </c>
@@ -8669,7 +8677,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A262" s="2" t="s">
         <v>491</v>
       </c>
@@ -8686,7 +8694,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A263" s="2" t="s">
         <v>491</v>
       </c>
@@ -8703,7 +8711,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A264" s="2" t="s">
         <v>491</v>
       </c>
@@ -8720,7 +8728,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A265" s="2" t="s">
         <v>491</v>
       </c>
@@ -8737,7 +8745,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A266" s="2" t="s">
         <v>491</v>
       </c>
@@ -8754,7 +8762,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A267" s="2" t="s">
         <v>491</v>
       </c>
@@ -8768,10 +8776,10 @@
         <v>496</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A268" s="2" t="s">
         <v>491</v>
       </c>
@@ -8788,7 +8796,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A269" s="2" t="s">
         <v>491</v>
       </c>
@@ -8805,7 +8813,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A270" s="2" t="s">
         <v>599</v>
       </c>
@@ -8822,7 +8830,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A271" s="2" t="s">
         <v>599</v>
       </c>
@@ -8839,7 +8847,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A272" s="2" t="s">
         <v>599</v>
       </c>
@@ -8856,66 +8864,66 @@
         <v>11</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A273" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B273" s="8" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C273" s="9" t="s">
         <v>607</v>
       </c>
-      <c r="C273" s="9" t="s">
+      <c r="D273" s="2" t="s">
         <v>608</v>
-      </c>
-      <c r="D273" s="2" t="s">
-        <v>609</v>
       </c>
       <c r="E273" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A274" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B274" s="8" t="s">
+        <v>609</v>
+      </c>
+      <c r="C274" s="9" t="s">
         <v>610</v>
       </c>
-      <c r="C274" s="9" t="s">
+      <c r="D274" s="2" t="s">
         <v>611</v>
-      </c>
-      <c r="D274" s="2" t="s">
-        <v>612</v>
       </c>
       <c r="E274" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A275" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B275" s="8" t="s">
+        <v>612</v>
+      </c>
+      <c r="C275" s="9" t="s">
         <v>613</v>
       </c>
-      <c r="C275" s="9" t="s">
-        <v>614</v>
-      </c>
       <c r="D275" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E275" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A276" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B276" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="C276" s="14" t="s">
         <v>615</v>
-      </c>
-      <c r="C276" s="14" t="s">
-        <v>616</v>
       </c>
       <c r="D276" s="2" t="s">
         <v>602</v>
@@ -8924,24 +8932,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A277" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B277" s="8" t="s">
+        <v>616</v>
+      </c>
+      <c r="C277" s="9" t="s">
         <v>617</v>
       </c>
-      <c r="C277" s="9" t="s">
+      <c r="D277" s="2" t="s">
         <v>618</v>
-      </c>
-      <c r="D277" s="2" t="s">
-        <v>619</v>
       </c>
       <c r="E277" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A278" s="2" t="s">
         <v>599</v>
       </c>
@@ -8952,13 +8960,13 @@
         <v>26090137</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E278" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A279" s="2" t="s">
         <v>599</v>
       </c>
@@ -8966,33 +8974,33 @@
         <v>585</v>
       </c>
       <c r="C279" s="9" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E279" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A280" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B280" s="8" t="s">
+        <v>621</v>
+      </c>
+      <c r="C280" s="9" t="s">
         <v>622</v>
       </c>
-      <c r="C280" s="9" t="s">
-        <v>623</v>
-      </c>
       <c r="D280" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E280" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A281" s="2" t="s">
         <v>599</v>
       </c>
@@ -9000,75 +9008,75 @@
         <v>295</v>
       </c>
       <c r="C281" s="9" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E281" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A282" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B282" s="8" t="s">
+        <v>624</v>
+      </c>
+      <c r="C282" s="9" t="s">
         <v>625</v>
       </c>
-      <c r="C282" s="9" t="s">
-        <v>626</v>
-      </c>
       <c r="D282" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E282" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A283" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B283" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="C283" s="9" t="s">
         <v>627</v>
       </c>
-      <c r="C283" s="9" t="s">
+      <c r="D283" s="2" t="s">
         <v>628</v>
-      </c>
-      <c r="D283" s="2" t="s">
-        <v>629</v>
       </c>
       <c r="E283" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A284" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B284" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="C284" s="9" t="s">
         <v>630</v>
       </c>
-      <c r="C284" s="9" t="s">
+      <c r="D284" s="2" t="s">
         <v>631</v>
-      </c>
-      <c r="D284" s="2" t="s">
-        <v>632</v>
       </c>
       <c r="E284" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A285" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B285" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="C285" s="9" t="s">
         <v>633</v>
-      </c>
-      <c r="C285" s="9" t="s">
-        <v>634</v>
       </c>
       <c r="D285" s="2" t="s">
         <v>185</v>
@@ -9077,32 +9085,32 @@
         <v>11</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A286" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B286" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="C286" s="9" t="s">
         <v>635</v>
       </c>
-      <c r="C286" s="9" t="s">
-        <v>636</v>
-      </c>
       <c r="D286" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E286" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A287" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B287" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="C287" s="9" t="s">
         <v>637</v>
-      </c>
-      <c r="C287" s="9" t="s">
-        <v>638</v>
       </c>
       <c r="D287" s="2" t="s">
         <v>185</v>
@@ -9111,41 +9119,41 @@
         <v>11</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A288" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B288" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="C288" s="9" t="s">
         <v>639</v>
       </c>
-      <c r="C288" s="9" t="s">
+      <c r="D288" s="2" t="s">
         <v>640</v>
-      </c>
-      <c r="D288" s="2" t="s">
-        <v>641</v>
       </c>
       <c r="E288" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A289" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B289" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="C289" s="9" t="s">
         <v>642</v>
       </c>
-      <c r="C289" s="9" t="s">
+      <c r="D289" s="2" t="s">
         <v>643</v>
-      </c>
-      <c r="D289" s="2" t="s">
-        <v>644</v>
       </c>
       <c r="E289" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A290" s="2" t="s">
         <v>599</v>
       </c>
@@ -9153,118 +9161,118 @@
         <v>5</v>
       </c>
       <c r="C290" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="D290" s="2" t="s">
         <v>645</v>
-      </c>
-      <c r="D290" s="2" t="s">
-        <v>646</v>
       </c>
       <c r="E290" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A291" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B291" s="8" t="s">
+        <v>646</v>
+      </c>
+      <c r="C291" s="9" t="s">
         <v>647</v>
       </c>
-      <c r="C291" s="9" t="s">
-        <v>648</v>
-      </c>
       <c r="D291" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E291" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A292" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B292" s="8" t="s">
+        <v>648</v>
+      </c>
+      <c r="C292" s="9" t="s">
         <v>649</v>
       </c>
-      <c r="C292" s="9" t="s">
-        <v>650</v>
-      </c>
       <c r="D292" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E292" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A293" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B293" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="C293" s="9" t="s">
         <v>651</v>
       </c>
-      <c r="C293" s="9" t="s">
-        <v>652</v>
-      </c>
       <c r="D293" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E293" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A294" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B294" s="8" t="s">
+        <v>652</v>
+      </c>
+      <c r="C294" s="9" t="s">
         <v>653</v>
       </c>
-      <c r="C294" s="9" t="s">
-        <v>654</v>
-      </c>
       <c r="D294" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E294" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A295" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B295" s="8" t="s">
+        <v>654</v>
+      </c>
+      <c r="C295" s="9" t="s">
         <v>655</v>
       </c>
-      <c r="C295" s="9" t="s">
+      <c r="D295" s="2" t="s">
         <v>656</v>
-      </c>
-      <c r="D295" s="2" t="s">
-        <v>657</v>
       </c>
       <c r="E295" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A296" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B296" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="C296" s="9" t="s">
         <v>658</v>
       </c>
-      <c r="C296" s="9" t="s">
-        <v>659</v>
-      </c>
       <c r="D296" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E296" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A297" s="2" t="s">
         <v>599</v>
       </c>
@@ -9272,33 +9280,33 @@
         <v>67</v>
       </c>
       <c r="C297" s="9" t="s">
+        <v>659</v>
+      </c>
+      <c r="D297" s="2" t="s">
         <v>660</v>
-      </c>
-      <c r="D297" s="2" t="s">
-        <v>661</v>
       </c>
       <c r="E297" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A298" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B298" s="8" t="s">
+        <v>661</v>
+      </c>
+      <c r="C298" s="9" t="s">
         <v>662</v>
       </c>
-      <c r="C298" s="9" t="s">
+      <c r="D298" s="2" t="s">
         <v>663</v>
-      </c>
-      <c r="D298" s="2" t="s">
-        <v>664</v>
       </c>
       <c r="E298" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A299" s="2" t="s">
         <v>599</v>
       </c>
@@ -9306,24 +9314,24 @@
         <v>61</v>
       </c>
       <c r="C299" s="9" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E299" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A300" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B300" s="8" t="s">
+        <v>665</v>
+      </c>
+      <c r="C300" s="9" t="s">
         <v>666</v>
-      </c>
-      <c r="C300" s="9" t="s">
-        <v>667</v>
       </c>
       <c r="D300" s="2" t="s">
         <v>602</v>
@@ -9332,75 +9340,75 @@
         <v>11</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A301" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B301" s="8" t="s">
+        <v>667</v>
+      </c>
+      <c r="C301" s="9" t="s">
         <v>668</v>
       </c>
-      <c r="C301" s="9" t="s">
-        <v>669</v>
-      </c>
       <c r="D301" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="E301" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A302" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B302" s="8" t="s">
+        <v>669</v>
+      </c>
+      <c r="C302" s="9" t="s">
         <v>670</v>
       </c>
-      <c r="C302" s="9" t="s">
-        <v>671</v>
-      </c>
       <c r="D302" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="E302" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A303" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B303" s="8" t="s">
+        <v>671</v>
+      </c>
+      <c r="C303" s="9" t="s">
         <v>672</v>
       </c>
-      <c r="C303" s="9" t="s">
-        <v>673</v>
-      </c>
       <c r="D303" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E303" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A304" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B304" s="8" t="s">
+        <v>673</v>
+      </c>
+      <c r="C304" s="9" t="s">
         <v>674</v>
       </c>
-      <c r="C304" s="9" t="s">
-        <v>675</v>
-      </c>
       <c r="D304" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E304" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A305" s="2" t="s">
         <v>599</v>
       </c>
@@ -9408,16 +9416,16 @@
         <v>12</v>
       </c>
       <c r="C305" s="9" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E305" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A306" s="2" t="s">
         <v>599</v>
       </c>
@@ -9425,16 +9433,16 @@
         <v>49</v>
       </c>
       <c r="C306" s="9" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E306" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A307" s="2" t="s">
         <v>599</v>
       </c>
@@ -9442,7 +9450,7 @@
         <v>34</v>
       </c>
       <c r="C307" s="9" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D307" s="2" t="s">
         <v>604</v>
@@ -9451,7 +9459,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A308" s="2" t="s">
         <v>599</v>
       </c>
@@ -9459,33 +9467,33 @@
         <v>347</v>
       </c>
       <c r="C308" s="9" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E308" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A309" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B309" s="8" t="s">
+        <v>679</v>
+      </c>
+      <c r="C309" s="9" t="s">
         <v>680</v>
       </c>
-      <c r="C309" s="9" t="s">
-        <v>681</v>
-      </c>
       <c r="D309" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E309" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A310" s="2" t="s">
         <v>599</v>
       </c>
@@ -9493,118 +9501,118 @@
         <v>131</v>
       </c>
       <c r="C310" s="9" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E310" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A311" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B311" s="8" t="s">
+        <v>682</v>
+      </c>
+      <c r="C311" s="9" t="s">
         <v>683</v>
       </c>
-      <c r="C311" s="9" t="s">
-        <v>684</v>
-      </c>
       <c r="D311" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E311" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A312" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B312" s="8" t="s">
+        <v>684</v>
+      </c>
+      <c r="C312" s="9" t="s">
         <v>685</v>
       </c>
-      <c r="C312" s="9" t="s">
+      <c r="D312" s="7" t="s">
         <v>686</v>
       </c>
-      <c r="D312" s="7" t="s">
-        <v>687</v>
-      </c>
       <c r="E312" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A313" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B313" s="8" t="s">
+        <v>687</v>
+      </c>
+      <c r="C313" s="9" t="s">
         <v>688</v>
       </c>
-      <c r="C313" s="9" t="s">
+      <c r="D313" s="7" t="s">
         <v>689</v>
       </c>
-      <c r="D313" s="7" t="s">
-        <v>690</v>
-      </c>
       <c r="E313" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A314" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B314" s="8" t="s">
+        <v>690</v>
+      </c>
+      <c r="C314" s="9" t="s">
         <v>691</v>
       </c>
-      <c r="C314" s="9" t="s">
-        <v>692</v>
-      </c>
       <c r="D314" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="E314" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A315" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B315" s="8" t="s">
+        <v>692</v>
+      </c>
+      <c r="C315" s="9" t="s">
         <v>693</v>
       </c>
-      <c r="C315" s="9" t="s">
-        <v>694</v>
-      </c>
       <c r="D315" s="7" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E315" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A316" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B316" s="8" t="s">
+        <v>694</v>
+      </c>
+      <c r="C316" s="9" t="s">
         <v>695</v>
       </c>
-      <c r="C316" s="9" t="s">
-        <v>696</v>
-      </c>
       <c r="D316" s="7" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E316" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A317" s="2" t="s">
         <v>599</v>
       </c>
@@ -9612,67 +9620,67 @@
         <v>210</v>
       </c>
       <c r="C317" s="9" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D317" s="7" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E317" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A318" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B318" s="8" t="s">
+        <v>697</v>
+      </c>
+      <c r="C318" s="9" t="s">
         <v>698</v>
       </c>
-      <c r="C318" s="9" t="s">
-        <v>699</v>
-      </c>
       <c r="D318" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E318" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A319" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B319" s="8" t="s">
+        <v>699</v>
+      </c>
+      <c r="C319" s="9" t="s">
         <v>700</v>
       </c>
-      <c r="C319" s="9" t="s">
-        <v>701</v>
-      </c>
       <c r="D319" s="7" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="E319" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A320" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B320" s="8" t="s">
+        <v>701</v>
+      </c>
+      <c r="C320" s="9" t="s">
         <v>702</v>
       </c>
-      <c r="C320" s="9" t="s">
-        <v>703</v>
-      </c>
       <c r="D320" s="7" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E320" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A321" s="2" t="s">
         <v>599</v>
       </c>
@@ -9680,16 +9688,16 @@
         <v>85</v>
       </c>
       <c r="C321" s="9" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="D321" s="7" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E321" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A322" s="2" t="s">
         <v>599</v>
       </c>
@@ -9697,67 +9705,67 @@
         <v>111</v>
       </c>
       <c r="C322" s="9" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D322" s="7" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E322" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A323" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B323" s="8" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C323" s="9" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D323" s="7" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="E323" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A324" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B324" s="8" t="s">
+        <v>706</v>
+      </c>
+      <c r="C324" s="9" t="s">
         <v>707</v>
       </c>
-      <c r="C324" s="9" t="s">
-        <v>708</v>
-      </c>
       <c r="D324" s="7" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="E324" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A325" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B325" s="8" t="s">
+        <v>708</v>
+      </c>
+      <c r="C325" s="9" t="s">
         <v>709</v>
       </c>
-      <c r="C325" s="9" t="s">
-        <v>710</v>
-      </c>
       <c r="D325" s="7" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E325" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A326" s="2" t="s">
         <v>599</v>
       </c>
@@ -9765,67 +9773,67 @@
         <v>241</v>
       </c>
       <c r="C326" s="9" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D326" s="7" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E326" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A327" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B327" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="C327" s="9" t="s">
         <v>712</v>
       </c>
-      <c r="C327" s="9" t="s">
-        <v>713</v>
-      </c>
       <c r="D327" s="7" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="E327" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A328" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B328" s="8" t="s">
+        <v>713</v>
+      </c>
+      <c r="C328" s="9" t="s">
         <v>714</v>
       </c>
-      <c r="C328" s="9" t="s">
-        <v>715</v>
-      </c>
       <c r="D328" s="7" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E328" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A329" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B329" s="8" t="s">
+        <v>715</v>
+      </c>
+      <c r="C329" s="9" t="s">
         <v>716</v>
       </c>
-      <c r="C329" s="9" t="s">
-        <v>717</v>
-      </c>
       <c r="D329" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="E329" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A330" s="2" t="s">
         <v>599</v>
       </c>
@@ -9833,16 +9841,16 @@
         <v>58</v>
       </c>
       <c r="C330" s="9" t="s">
+        <v>717</v>
+      </c>
+      <c r="D330" s="7" t="s">
         <v>718</v>
       </c>
-      <c r="D330" s="7" t="s">
-        <v>719</v>
-      </c>
       <c r="E330" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A331" s="2" t="s">
         <v>599</v>
       </c>
@@ -9850,152 +9858,152 @@
         <v>512</v>
       </c>
       <c r="C331" s="9" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D331" s="7" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E331" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A332" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B332" s="8" t="s">
+        <v>720</v>
+      </c>
+      <c r="C332" s="9" t="s">
         <v>721</v>
       </c>
-      <c r="C332" s="9" t="s">
-        <v>722</v>
-      </c>
       <c r="D332" s="7" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E332" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A333" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B333" s="8" t="s">
+        <v>722</v>
+      </c>
+      <c r="C333" s="9" t="s">
         <v>723</v>
       </c>
-      <c r="C333" s="9" t="s">
-        <v>724</v>
-      </c>
       <c r="D333" s="7" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E333" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A334" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B334" s="8" t="s">
+        <v>724</v>
+      </c>
+      <c r="C334" s="9" t="s">
         <v>725</v>
       </c>
-      <c r="C334" s="9" t="s">
-        <v>726</v>
-      </c>
       <c r="D334" s="7" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E334" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A335" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B335" s="8" t="s">
+        <v>726</v>
+      </c>
+      <c r="C335" s="9" t="s">
         <v>727</v>
       </c>
-      <c r="C335" s="9" t="s">
-        <v>728</v>
-      </c>
       <c r="D335" s="7" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E335" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A336" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B336" s="8" t="s">
+        <v>728</v>
+      </c>
+      <c r="C336" s="9" t="s">
         <v>729</v>
       </c>
-      <c r="C336" s="9" t="s">
-        <v>730</v>
-      </c>
       <c r="D336" s="7" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E336" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A337" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B337" s="8" t="s">
+        <v>730</v>
+      </c>
+      <c r="C337" s="9" t="s">
         <v>731</v>
       </c>
-      <c r="C337" s="9" t="s">
-        <v>732</v>
-      </c>
       <c r="D337" s="7" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E337" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A338" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B338" s="8" t="s">
+        <v>732</v>
+      </c>
+      <c r="C338" s="9" t="s">
         <v>733</v>
       </c>
-      <c r="C338" s="9" t="s">
-        <v>734</v>
-      </c>
       <c r="D338" s="7" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E338" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A339" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B339" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="C339" s="9" t="s">
         <v>735</v>
       </c>
-      <c r="C339" s="9" t="s">
-        <v>736</v>
-      </c>
       <c r="D339" s="7" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E339" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A340" s="2" t="s">
         <v>599</v>
       </c>
@@ -10003,16 +10011,16 @@
         <v>582</v>
       </c>
       <c r="C340" s="9" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D340" s="7" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E340" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A341" s="2" t="s">
         <v>599</v>
       </c>
@@ -10020,50 +10028,50 @@
         <v>204</v>
       </c>
       <c r="C341" s="9" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D341" s="7" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="E341" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A342" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B342" s="8" t="s">
+        <v>738</v>
+      </c>
+      <c r="C342" s="9" t="s">
         <v>739</v>
       </c>
-      <c r="C342" s="9" t="s">
-        <v>740</v>
-      </c>
       <c r="D342" s="7" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E342" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A343" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B343" s="8" t="s">
+        <v>740</v>
+      </c>
+      <c r="C343" s="9" t="s">
         <v>741</v>
       </c>
-      <c r="C343" s="9" t="s">
-        <v>742</v>
-      </c>
       <c r="D343" s="7" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E343" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A344" s="2" t="s">
         <v>599</v>
       </c>
@@ -10071,7 +10079,7 @@
         <v>317</v>
       </c>
       <c r="C344" s="9" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D344" s="7" t="s">
         <v>602</v>
@@ -10080,219 +10088,219 @@
         <v>66</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A345" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B345" s="8" t="s">
+        <v>743</v>
+      </c>
+      <c r="C345" s="9" t="s">
         <v>744</v>
       </c>
-      <c r="C345" s="9" t="s">
-        <v>745</v>
-      </c>
       <c r="D345" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="E345" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A346" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B346" s="8" t="s">
+        <v>745</v>
+      </c>
+      <c r="C346" s="9" t="s">
         <v>746</v>
       </c>
-      <c r="C346" s="9" t="s">
-        <v>747</v>
-      </c>
       <c r="D346" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E346" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A347" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B347" s="8" t="s">
+        <v>747</v>
+      </c>
+      <c r="C347" s="9" t="s">
         <v>748</v>
       </c>
-      <c r="C347" s="9" t="s">
-        <v>749</v>
-      </c>
       <c r="D347" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E347" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A348" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B348" s="8" t="s">
+        <v>749</v>
+      </c>
+      <c r="C348" s="9" t="s">
         <v>750</v>
       </c>
-      <c r="C348" s="9" t="s">
-        <v>751</v>
-      </c>
       <c r="D348" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E348" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A349" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B349" s="8" t="s">
+        <v>751</v>
+      </c>
+      <c r="C349" s="9" t="s">
         <v>752</v>
       </c>
-      <c r="C349" s="9" t="s">
-        <v>753</v>
-      </c>
       <c r="D349" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E349" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A350" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B350" s="15" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C350" s="9">
         <v>26090400</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E350" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A351" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B351" s="8" t="s">
+        <v>754</v>
+      </c>
+      <c r="C351" s="9" t="s">
         <v>755</v>
       </c>
-      <c r="C351" s="9" t="s">
-        <v>756</v>
-      </c>
       <c r="D351" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E351" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A352" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B352" s="8" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C352" s="9">
         <v>26090296</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E352" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A353" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B353" s="8" t="s">
+        <v>757</v>
+      </c>
+      <c r="C353" s="9" t="s">
         <v>758</v>
       </c>
-      <c r="C353" s="9" t="s">
-        <v>759</v>
-      </c>
       <c r="D353" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E353" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A354" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B354" s="8" t="s">
+        <v>759</v>
+      </c>
+      <c r="C354" s="9" t="s">
         <v>760</v>
       </c>
-      <c r="C354" s="9" t="s">
-        <v>761</v>
-      </c>
       <c r="D354" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E354" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A355" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B355" s="8" t="s">
+        <v>761</v>
+      </c>
+      <c r="C355" s="9" t="s">
         <v>762</v>
       </c>
-      <c r="C355" s="9" t="s">
-        <v>763</v>
-      </c>
       <c r="D355" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="E355" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A356" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B356" s="8" t="s">
+        <v>763</v>
+      </c>
+      <c r="C356" s="9" t="s">
         <v>764</v>
       </c>
-      <c r="C356" s="9" t="s">
-        <v>765</v>
-      </c>
       <c r="D356" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E356" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A357" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B357" s="8" t="s">
+        <v>765</v>
+      </c>
+      <c r="C357" s="9" t="s">
         <v>766</v>
-      </c>
-      <c r="C357" s="9" t="s">
-        <v>767</v>
       </c>
       <c r="D357" s="2" t="s">
         <v>604</v>
@@ -10301,7 +10309,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A358" s="2" t="s">
         <v>599</v>
       </c>
@@ -10309,16 +10317,16 @@
         <v>5</v>
       </c>
       <c r="C358" s="9" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E358" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A359" s="2" t="s">
         <v>599</v>
       </c>
@@ -10326,84 +10334,84 @@
         <v>547</v>
       </c>
       <c r="C359" s="9" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="E359" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A360" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B360" s="8" t="s">
+        <v>769</v>
+      </c>
+      <c r="C360" s="9" t="s">
         <v>770</v>
       </c>
-      <c r="C360" s="9" t="s">
+      <c r="D360" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="E360" s="16" t="s">
         <v>771</v>
       </c>
-      <c r="D360" s="2" t="s">
-        <v>690</v>
-      </c>
-      <c r="E360" s="16" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="361" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A361" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B361" s="8" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C361" s="9">
         <v>26090423</v>
       </c>
       <c r="D361" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E361" s="2" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A362" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B362" s="8" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C362" s="9">
         <v>26090218</v>
       </c>
       <c r="D362" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E362" s="2" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A363" s="17" t="s">
         <v>599</v>
       </c>
       <c r="B363" s="18" t="s">
+        <v>773</v>
+      </c>
+      <c r="C363" s="19" t="s">
         <v>774</v>
       </c>
-      <c r="C363" s="19" t="s">
-        <v>775</v>
-      </c>
       <c r="D363" s="17" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E363" s="17" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A364" s="17" t="s">
         <v>599</v>
       </c>
@@ -10420,41 +10428,41 @@
         <v>78</v>
       </c>
     </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A365" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B365" s="8" t="s">
+        <v>775</v>
+      </c>
+      <c r="C365" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="C365" s="9" t="s">
+      <c r="D365" s="2" t="s">
         <v>777</v>
       </c>
-      <c r="D365" s="2" t="s">
-        <v>778</v>
-      </c>
       <c r="E365" s="2" t="s">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A366" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B366" s="8" t="s">
+        <v>778</v>
+      </c>
+      <c r="C366" s="9" t="s">
         <v>779</v>
       </c>
-      <c r="C366" s="9" t="s">
-        <v>780</v>
-      </c>
       <c r="D366" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E366" s="2" t="s">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A367" s="2" t="s">
         <v>599</v>
       </c>
@@ -10462,33 +10470,33 @@
         <v>573</v>
       </c>
       <c r="C367" s="9" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="D367" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E367" s="2" t="s">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A368" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B368" s="8" t="s">
+        <v>781</v>
+      </c>
+      <c r="C368" s="9" t="s">
         <v>782</v>
-      </c>
-      <c r="C368" s="9" t="s">
-        <v>783</v>
       </c>
       <c r="D368" s="2" t="s">
         <v>604</v>
       </c>
       <c r="E368" s="2" t="s">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A369" s="2" t="s">
         <v>599</v>
       </c>
@@ -10496,16 +10504,16 @@
         <v>377</v>
       </c>
       <c r="C369" s="9" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="D369" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E369" s="2" t="s">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A370" s="2" t="s">
         <v>599</v>
       </c>
@@ -10519,10 +10527,10 @@
         <v>604</v>
       </c>
       <c r="E370" s="2" t="s">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A371" s="2" t="s">
         <v>599</v>
       </c>
@@ -10530,84 +10538,84 @@
         <v>295</v>
       </c>
       <c r="C371" s="9" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="D371" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E371" s="2" t="s">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A372" s="20" t="s">
         <v>599</v>
       </c>
       <c r="B372" s="21" t="s">
+        <v>785</v>
+      </c>
+      <c r="C372" s="22" t="s">
         <v>786</v>
       </c>
-      <c r="C372" s="22" t="s">
-        <v>787</v>
-      </c>
       <c r="D372" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="E372" s="20" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A373" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B373" s="8" t="s">
+        <v>787</v>
+      </c>
+      <c r="C373" s="9" t="s">
         <v>788</v>
       </c>
-      <c r="C373" s="9" t="s">
-        <v>789</v>
-      </c>
       <c r="D373" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="E373" s="2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A374" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B374" s="8" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C374" s="9" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D374" s="7" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E374" s="2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A375" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B375" s="8" t="s">
+        <v>790</v>
+      </c>
+      <c r="C375" s="9" t="s">
         <v>791</v>
       </c>
-      <c r="C375" s="9" t="s">
+      <c r="D375" s="7" t="s">
         <v>792</v>
-      </c>
-      <c r="D375" s="7" t="s">
-        <v>793</v>
       </c>
       <c r="E375" s="2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A376" s="2" t="s">
         <v>599</v>
       </c>
@@ -10615,140 +10623,140 @@
         <v>241</v>
       </c>
       <c r="C376" s="9" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D376" s="7" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E376" s="2" t="s">
-        <v>1201</v>
-      </c>
-    </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A377" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B377" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="C377" s="23" t="s">
         <v>795</v>
       </c>
-      <c r="C377" s="23" t="s">
+      <c r="D377" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="E377" s="2" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A378" s="2" t="s">
         <v>796</v>
       </c>
-      <c r="D377" s="2" t="s">
-        <v>719</v>
-      </c>
-      <c r="E377" s="2" t="s">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A378" s="2" t="s">
+      <c r="B378" s="8" t="s">
         <v>797</v>
       </c>
-      <c r="B378" s="8" t="s">
+      <c r="C378" s="9" t="s">
         <v>798</v>
       </c>
-      <c r="C378" s="9" t="s">
+      <c r="D378" s="2" t="s">
         <v>799</v>
-      </c>
-      <c r="D378" s="2" t="s">
-        <v>800</v>
       </c>
       <c r="E378" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A379" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B379" s="8" t="s">
+        <v>800</v>
+      </c>
+      <c r="C379" s="9" t="s">
         <v>801</v>
       </c>
-      <c r="C379" s="9" t="s">
+      <c r="D379" s="2" t="s">
         <v>802</v>
-      </c>
-      <c r="D379" s="2" t="s">
-        <v>803</v>
       </c>
       <c r="E379" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A380" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B380" s="8" t="s">
         <v>34</v>
       </c>
       <c r="C380" s="9" t="s">
+        <v>803</v>
+      </c>
+      <c r="D380" s="2" t="s">
         <v>804</v>
-      </c>
-      <c r="D380" s="2" t="s">
-        <v>805</v>
       </c>
       <c r="E380" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A381" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B381" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="C381" s="9" t="s">
         <v>806</v>
       </c>
-      <c r="C381" s="9" t="s">
-        <v>807</v>
-      </c>
       <c r="D381" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="E381" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A382" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B382" s="8" t="s">
         <v>260</v>
       </c>
       <c r="C382" s="9" t="s">
+        <v>807</v>
+      </c>
+      <c r="D382" s="2" t="s">
         <v>808</v>
-      </c>
-      <c r="D382" s="2" t="s">
-        <v>809</v>
       </c>
       <c r="E382" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A383" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B383" s="8" t="s">
+        <v>809</v>
+      </c>
+      <c r="C383" s="9" t="s">
         <v>810</v>
       </c>
-      <c r="C383" s="9" t="s">
+      <c r="D383" s="7" t="s">
         <v>811</v>
       </c>
-      <c r="D383" s="7" t="s">
+      <c r="E383" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A384" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="B384" s="8" t="s">
         <v>812</v>
-      </c>
-      <c r="E383" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A384" s="2" t="s">
-        <v>797</v>
-      </c>
-      <c r="B384" s="8" t="s">
-        <v>813</v>
       </c>
       <c r="C384" s="9"/>
       <c r="D384" s="7"/>
@@ -10756,134 +10764,134 @@
         <v>33</v>
       </c>
     </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A385" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B385" s="8" t="s">
         <v>52</v>
       </c>
       <c r="C385" s="9" t="s">
+        <v>813</v>
+      </c>
+      <c r="D385" s="7" t="s">
         <v>814</v>
       </c>
-      <c r="D385" s="7" t="s">
-        <v>815</v>
-      </c>
       <c r="E385" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A386" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B386" s="8" t="s">
         <v>37</v>
       </c>
       <c r="C386" s="9" t="s">
+        <v>815</v>
+      </c>
+      <c r="D386" s="7" t="s">
         <v>816</v>
       </c>
-      <c r="D386" s="7" t="s">
-        <v>817</v>
-      </c>
       <c r="E386" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A387" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B387" s="8" t="s">
         <v>52</v>
       </c>
       <c r="C387" s="9" t="s">
+        <v>817</v>
+      </c>
+      <c r="D387" s="7" t="s">
         <v>818</v>
       </c>
-      <c r="D387" s="7" t="s">
-        <v>819</v>
-      </c>
       <c r="E387" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A388" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B388" s="8" t="s">
         <v>403</v>
       </c>
       <c r="C388" s="9" t="s">
+        <v>819</v>
+      </c>
+      <c r="D388" s="7" t="s">
         <v>820</v>
       </c>
-      <c r="D388" s="7" t="s">
+      <c r="E388" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A389" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="B389" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="C389" s="9" t="s">
         <v>821</v>
       </c>
-      <c r="E388" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A389" s="2" t="s">
-        <v>797</v>
-      </c>
-      <c r="B389" s="8" t="s">
-        <v>635</v>
-      </c>
-      <c r="C389" s="9" t="s">
+      <c r="D389" s="7" t="s">
         <v>822</v>
       </c>
-      <c r="D389" s="7" t="s">
+      <c r="E389" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A390" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="B390" s="8" t="s">
         <v>823</v>
       </c>
-      <c r="E389" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A390" s="2" t="s">
-        <v>797</v>
-      </c>
-      <c r="B390" s="8" t="s">
+      <c r="C390" s="9" t="s">
         <v>824</v>
       </c>
-      <c r="C390" s="9" t="s">
+      <c r="D390" s="7" t="s">
         <v>825</v>
       </c>
-      <c r="D390" s="7" t="s">
+      <c r="E390" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A391" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="B391" s="8" t="s">
         <v>826</v>
       </c>
-      <c r="E390" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A391" s="2" t="s">
-        <v>797</v>
-      </c>
-      <c r="B391" s="8" t="s">
+      <c r="C391" s="9" t="s">
         <v>827</v>
       </c>
-      <c r="C391" s="9" t="s">
+      <c r="D391" s="7" t="s">
         <v>828</v>
       </c>
-      <c r="D391" s="7" t="s">
+      <c r="E391" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="392" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A392" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="B392" s="8" t="s">
         <v>829</v>
       </c>
-      <c r="E391" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A392" s="2" t="s">
-        <v>797</v>
-      </c>
-      <c r="B392" s="8" t="s">
+      <c r="C392" s="9" t="s">
         <v>830</v>
-      </c>
-      <c r="C392" s="9" t="s">
-        <v>831</v>
       </c>
       <c r="D392" s="7" t="s">
         <v>578</v>
@@ -10892,128 +10900,128 @@
         <v>33</v>
       </c>
     </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A393" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B393" s="8" t="s">
         <v>49</v>
       </c>
       <c r="C393" s="9" t="s">
+        <v>831</v>
+      </c>
+      <c r="D393" s="7" t="s">
         <v>832</v>
       </c>
-      <c r="D393" s="7" t="s">
-        <v>833</v>
-      </c>
       <c r="E393" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A394" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B394" s="2" t="s">
         <v>129</v>
       </c>
       <c r="C394" s="9" t="s">
+        <v>833</v>
+      </c>
+      <c r="D394" s="7" t="s">
         <v>834</v>
       </c>
-      <c r="D394" s="7" t="s">
-        <v>835</v>
-      </c>
       <c r="E394" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A395" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B395" s="8" t="s">
         <v>241</v>
       </c>
       <c r="C395" s="9" t="s">
+        <v>835</v>
+      </c>
+      <c r="D395" s="7" t="s">
         <v>836</v>
       </c>
-      <c r="D395" s="7" t="s">
-        <v>837</v>
-      </c>
       <c r="E395" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A396" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B396" s="8" t="s">
         <v>196</v>
       </c>
       <c r="C396" s="9" t="s">
+        <v>837</v>
+      </c>
+      <c r="D396" s="7" t="s">
         <v>838</v>
       </c>
-      <c r="D396" s="7" t="s">
-        <v>839</v>
-      </c>
       <c r="E396" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A397" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B397" s="8" t="s">
         <v>193</v>
       </c>
       <c r="C397" s="9" t="s">
+        <v>839</v>
+      </c>
+      <c r="D397" s="7" t="s">
         <v>840</v>
       </c>
-      <c r="D397" s="7" t="s">
-        <v>841</v>
-      </c>
       <c r="E397" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A398" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B398" s="8" t="s">
         <v>49</v>
       </c>
       <c r="C398" s="9" t="s">
+        <v>841</v>
+      </c>
+      <c r="D398" s="7" t="s">
         <v>842</v>
       </c>
-      <c r="D398" s="7" t="s">
-        <v>843</v>
-      </c>
       <c r="E398" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A399" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B399" s="8" t="s">
         <v>131</v>
       </c>
       <c r="C399" s="9" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="D399" s="2" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E399" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A400" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B400" s="8" t="s">
         <v>596</v>
@@ -11022,253 +11030,253 @@
         <v>26100204</v>
       </c>
       <c r="D400" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="E400" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A401" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B401" s="8" t="s">
         <v>34</v>
       </c>
       <c r="C401" s="9" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="D401" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="E401" s="6" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A402" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B402" s="8" t="s">
+        <v>845</v>
+      </c>
+      <c r="C402" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="C402" s="9" t="s">
-        <v>847</v>
-      </c>
       <c r="D402" s="7" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="E402" s="6" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="403" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A403" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B403" s="8" t="s">
         <v>5</v>
       </c>
       <c r="C403" s="9" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="D403" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="E403" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A404" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B404" s="8" t="s">
+        <v>848</v>
+      </c>
+      <c r="C404" s="9" t="s">
         <v>849</v>
       </c>
-      <c r="C404" s="9" t="s">
+      <c r="D404" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="E404" s="2" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="405" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A405" s="2" t="s">
         <v>850</v>
       </c>
-      <c r="D404" s="2" t="s">
-        <v>803</v>
-      </c>
-      <c r="E404" s="2" t="s">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A405" s="2" t="s">
+      <c r="B405" s="8" t="s">
         <v>851</v>
       </c>
-      <c r="B405" s="8" t="s">
+      <c r="C405" s="9" t="s">
         <v>852</v>
       </c>
-      <c r="C405" s="9" t="s">
+      <c r="D405" s="2" t="s">
         <v>853</v>
-      </c>
-      <c r="D405" s="2" t="s">
-        <v>854</v>
       </c>
       <c r="E405" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A406" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B406" s="8" t="s">
+        <v>854</v>
+      </c>
+      <c r="C406" s="9" t="s">
         <v>855</v>
       </c>
-      <c r="C406" s="9" t="s">
+      <c r="D406" s="2" t="s">
         <v>856</v>
-      </c>
-      <c r="D406" s="2" t="s">
-        <v>857</v>
       </c>
       <c r="E406" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A407" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B407" s="8" t="s">
+        <v>857</v>
+      </c>
+      <c r="C407" s="9" t="s">
         <v>858</v>
       </c>
-      <c r="C407" s="9" t="s">
-        <v>859</v>
-      </c>
       <c r="D407" s="2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="E407" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="408" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A408" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B408" s="8" t="s">
         <v>34</v>
       </c>
       <c r="C408" s="9" t="s">
+        <v>859</v>
+      </c>
+      <c r="D408" s="2" t="s">
         <v>860</v>
-      </c>
-      <c r="D408" s="2" t="s">
-        <v>861</v>
       </c>
       <c r="E408" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A409" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B409" s="8" t="s">
         <v>61</v>
       </c>
       <c r="C409" s="9" t="s">
+        <v>861</v>
+      </c>
+      <c r="D409" s="2" t="s">
         <v>862</v>
-      </c>
-      <c r="D409" s="2" t="s">
-        <v>863</v>
       </c>
       <c r="E409" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="410" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A410" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B410" s="8" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C410" s="9" t="s">
+        <v>863</v>
+      </c>
+      <c r="D410" s="2" t="s">
         <v>864</v>
-      </c>
-      <c r="D410" s="2" t="s">
-        <v>865</v>
       </c>
       <c r="E410" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A411" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B411" s="8" t="s">
+        <v>865</v>
+      </c>
+      <c r="C411" s="9" t="s">
         <v>866</v>
       </c>
-      <c r="C411" s="9" t="s">
-        <v>867</v>
-      </c>
       <c r="D411" s="2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="E411" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A412" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B412" s="8" t="s">
+        <v>867</v>
+      </c>
+      <c r="C412" s="9" t="s">
         <v>868</v>
       </c>
-      <c r="C412" s="9" t="s">
+      <c r="D412" s="2" t="s">
         <v>869</v>
-      </c>
-      <c r="D412" s="2" t="s">
-        <v>870</v>
       </c>
       <c r="E412" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A413" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B413" s="8" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C413" s="9" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="D413" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="E413" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="414" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A414" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B414" s="8" t="s">
+        <v>871</v>
+      </c>
+      <c r="C414" s="9" t="s">
         <v>872</v>
       </c>
-      <c r="C414" s="9" t="s">
+      <c r="D414" s="2" t="s">
         <v>873</v>
-      </c>
-      <c r="D414" s="2" t="s">
-        <v>874</v>
       </c>
       <c r="E414" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="415" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A415" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B415" s="8" t="s">
         <v>451</v>
@@ -11277,1001 +11285,1001 @@
         <v>26110231</v>
       </c>
       <c r="D415" s="7" t="s">
+        <v>874</v>
+      </c>
+      <c r="E415" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="416" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A416" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="B416" s="8" t="s">
         <v>875</v>
       </c>
-      <c r="E415" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="416" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A416" s="2" t="s">
-        <v>851</v>
-      </c>
-      <c r="B416" s="8" t="s">
+      <c r="C416" s="9" t="s">
         <v>876</v>
       </c>
-      <c r="C416" s="9" t="s">
+      <c r="D416" s="7" t="s">
         <v>877</v>
       </c>
-      <c r="D416" s="7" t="s">
+      <c r="E416" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="417" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A417" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="B417" s="8" t="s">
         <v>878</v>
       </c>
-      <c r="E416" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="417" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A417" s="2" t="s">
-        <v>851</v>
-      </c>
-      <c r="B417" s="8" t="s">
+      <c r="C417" s="9" t="s">
         <v>879</v>
       </c>
-      <c r="C417" s="9" t="s">
+      <c r="D417" s="7" t="s">
         <v>880</v>
       </c>
-      <c r="D417" s="7" t="s">
-        <v>881</v>
-      </c>
       <c r="E417" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A418" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B418" s="8" t="s">
         <v>253</v>
       </c>
       <c r="C418" s="9" t="s">
+        <v>881</v>
+      </c>
+      <c r="D418" s="7" t="s">
         <v>882</v>
       </c>
-      <c r="D418" s="7" t="s">
+      <c r="E418" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="419" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A419" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="B419" s="8" t="s">
         <v>883</v>
       </c>
-      <c r="E418" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A419" s="2" t="s">
-        <v>851</v>
-      </c>
-      <c r="B419" s="8" t="s">
+      <c r="C419" s="9" t="s">
         <v>884</v>
       </c>
-      <c r="C419" s="9" t="s">
+      <c r="D419" s="7" t="s">
         <v>885</v>
       </c>
-      <c r="D419" s="7" t="s">
+      <c r="E419" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="420" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A420" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="B420" s="8" t="s">
         <v>886</v>
       </c>
-      <c r="E419" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="420" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A420" s="2" t="s">
-        <v>851</v>
-      </c>
-      <c r="B420" s="8" t="s">
+      <c r="C420" s="9" t="s">
         <v>887</v>
       </c>
-      <c r="C420" s="9" t="s">
+      <c r="D420" s="7" t="s">
+        <v>856</v>
+      </c>
+      <c r="E420" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A421" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="B421" s="8" t="s">
         <v>888</v>
       </c>
-      <c r="D420" s="7" t="s">
-        <v>857</v>
-      </c>
-      <c r="E420" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A421" s="2" t="s">
-        <v>851</v>
-      </c>
-      <c r="B421" s="8" t="s">
+      <c r="C421" s="9" t="s">
         <v>889</v>
       </c>
-      <c r="C421" s="9" t="s">
+      <c r="D421" s="7" t="s">
         <v>890</v>
       </c>
-      <c r="D421" s="7" t="s">
+      <c r="E421" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="422" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A422" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="B422" s="8" t="s">
         <v>891</v>
       </c>
-      <c r="E421" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A422" s="2" t="s">
-        <v>851</v>
-      </c>
-      <c r="B422" s="8" t="s">
+      <c r="C422" s="9" t="s">
         <v>892</v>
       </c>
-      <c r="C422" s="9" t="s">
+      <c r="D422" s="7" t="s">
         <v>893</v>
       </c>
-      <c r="D422" s="7" t="s">
-        <v>894</v>
-      </c>
       <c r="E422" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A423" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B423" s="8" t="s">
         <v>121</v>
       </c>
       <c r="C423" s="9" t="s">
+        <v>894</v>
+      </c>
+      <c r="D423" s="7" t="s">
         <v>895</v>
       </c>
-      <c r="D423" s="7" t="s">
+      <c r="E423" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A424" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="B424" s="8" t="s">
         <v>896</v>
       </c>
-      <c r="E423" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A424" s="2" t="s">
-        <v>851</v>
-      </c>
-      <c r="B424" s="8" t="s">
+      <c r="C424" s="9" t="s">
         <v>897</v>
       </c>
-      <c r="C424" s="9" t="s">
+      <c r="D424" s="7" t="s">
         <v>898</v>
       </c>
-      <c r="D424" s="7" t="s">
-        <v>899</v>
-      </c>
       <c r="E424" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A425" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B425" s="8" t="s">
         <v>340</v>
       </c>
       <c r="C425" s="9" t="s">
+        <v>899</v>
+      </c>
+      <c r="D425" s="7" t="s">
         <v>900</v>
       </c>
-      <c r="D425" s="7" t="s">
+      <c r="E425" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="426" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A426" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="B426" s="8" t="s">
+        <v>857</v>
+      </c>
+      <c r="C426" s="9" t="s">
         <v>901</v>
       </c>
-      <c r="E425" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A426" s="2" t="s">
-        <v>851</v>
-      </c>
-      <c r="B426" s="8" t="s">
-        <v>858</v>
-      </c>
-      <c r="C426" s="9" t="s">
+      <c r="D426" s="7" t="s">
         <v>902</v>
       </c>
-      <c r="D426" s="7" t="s">
+      <c r="E426" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="427" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A427" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="B427" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="E426" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A427" s="2" t="s">
-        <v>851</v>
-      </c>
-      <c r="B427" s="8" t="s">
+      <c r="C427" s="9" t="s">
         <v>904</v>
       </c>
-      <c r="C427" s="9" t="s">
+      <c r="D427" s="7" t="s">
         <v>905</v>
       </c>
-      <c r="D427" s="7" t="s">
-        <v>906</v>
-      </c>
       <c r="E427" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="428" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A428" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B428" s="8" t="s">
         <v>241</v>
       </c>
       <c r="C428" s="9" t="s">
+        <v>906</v>
+      </c>
+      <c r="D428" s="7" t="s">
         <v>907</v>
       </c>
-      <c r="D428" s="7" t="s">
+      <c r="E428" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="429" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A429" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="B429" s="8" t="s">
         <v>908</v>
       </c>
-      <c r="E428" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A429" s="2" t="s">
-        <v>851</v>
-      </c>
-      <c r="B429" s="8" t="s">
+      <c r="C429" s="9" t="s">
         <v>909</v>
       </c>
-      <c r="C429" s="9" t="s">
+      <c r="D429" s="7" t="s">
         <v>910</v>
       </c>
-      <c r="D429" s="7" t="s">
-        <v>911</v>
-      </c>
       <c r="E429" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="430" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A430" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B430" s="8" t="s">
         <v>55</v>
       </c>
       <c r="C430" s="9" t="s">
+        <v>911</v>
+      </c>
+      <c r="D430" s="7" t="s">
         <v>912</v>
       </c>
-      <c r="D430" s="7" t="s">
-        <v>913</v>
-      </c>
       <c r="E430" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A431" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B431" s="8" t="s">
         <v>596</v>
       </c>
       <c r="C431" s="9" t="s">
+        <v>913</v>
+      </c>
+      <c r="D431" s="7" t="s">
         <v>914</v>
       </c>
-      <c r="D431" s="7" t="s">
+      <c r="E431" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A432" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="B432" s="8" t="s">
         <v>915</v>
       </c>
-      <c r="E431" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="432" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A432" s="2" t="s">
-        <v>851</v>
-      </c>
-      <c r="B432" s="8" t="s">
+      <c r="C432" s="9" t="s">
         <v>916</v>
       </c>
-      <c r="C432" s="9" t="s">
+      <c r="D432" s="7" t="s">
         <v>917</v>
       </c>
-      <c r="D432" s="7" t="s">
-        <v>918</v>
-      </c>
       <c r="E432" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A433" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B433" s="8" t="s">
         <v>204</v>
       </c>
       <c r="C433" s="9" t="s">
+        <v>918</v>
+      </c>
+      <c r="D433" s="7" t="s">
         <v>919</v>
       </c>
-      <c r="D433" s="7" t="s">
+      <c r="E433" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="434" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A434" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="B434" s="8" t="s">
         <v>920</v>
       </c>
-      <c r="E433" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A434" s="2" t="s">
-        <v>851</v>
-      </c>
-      <c r="B434" s="8" t="s">
+      <c r="C434" s="9" t="s">
         <v>921</v>
       </c>
-      <c r="C434" s="9" t="s">
+      <c r="D434" s="7" t="s">
         <v>922</v>
       </c>
-      <c r="D434" s="7" t="s">
+      <c r="E434" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="435" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A435" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="B435" s="8" t="s">
+        <v>665</v>
+      </c>
+      <c r="C435" s="9" t="s">
         <v>923</v>
       </c>
-      <c r="E434" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A435" s="2" t="s">
-        <v>851</v>
-      </c>
-      <c r="B435" s="8" t="s">
-        <v>666</v>
-      </c>
-      <c r="C435" s="9" t="s">
+      <c r="D435" s="7" t="s">
         <v>924</v>
       </c>
-      <c r="D435" s="7" t="s">
-        <v>925</v>
-      </c>
       <c r="E435" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A436" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B436" s="8" t="s">
         <v>193</v>
       </c>
       <c r="C436" s="9" t="s">
+        <v>925</v>
+      </c>
+      <c r="D436" s="7" t="s">
         <v>926</v>
       </c>
-      <c r="D436" s="7" t="s">
-        <v>927</v>
-      </c>
       <c r="E436" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="437" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A437" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B437" s="8" t="s">
         <v>241</v>
       </c>
       <c r="C437" s="9" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E437" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="438" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A438" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B438" s="8" t="s">
+        <v>928</v>
+      </c>
+      <c r="C438" s="9" t="s">
         <v>929</v>
       </c>
-      <c r="C438" s="9" t="s">
-        <v>930</v>
-      </c>
       <c r="D438" s="2" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="E438" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A439" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B439" s="8" t="s">
+        <v>930</v>
+      </c>
+      <c r="C439" s="9" t="s">
         <v>931</v>
       </c>
-      <c r="C439" s="9" t="s">
-        <v>932</v>
-      </c>
       <c r="D439" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="E439" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="440" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A440" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B440" s="8" t="s">
+        <v>932</v>
+      </c>
+      <c r="C440" s="9" t="s">
         <v>933</v>
       </c>
-      <c r="C440" s="9" t="s">
-        <v>934</v>
-      </c>
       <c r="D440" s="2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="E440" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A441" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B441" s="8" t="s">
+        <v>934</v>
+      </c>
+      <c r="C441" s="9" t="s">
         <v>935</v>
       </c>
-      <c r="C441" s="9" t="s">
-        <v>936</v>
-      </c>
       <c r="D441" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="E441" s="6" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A442" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B442" s="8" t="s">
+        <v>936</v>
+      </c>
+      <c r="C442" s="9" t="s">
         <v>937</v>
       </c>
-      <c r="C442" s="9" t="s">
+      <c r="D442" s="7" t="s">
+        <v>862</v>
+      </c>
+      <c r="E442" s="6" t="s">
         <v>938</v>
       </c>
-      <c r="D442" s="7" t="s">
-        <v>863</v>
-      </c>
-      <c r="E442" s="6" t="s">
+    </row>
+    <row r="443" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A443" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="B443" s="8" t="s">
         <v>939</v>
       </c>
-    </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A443" s="2" t="s">
-        <v>851</v>
-      </c>
-      <c r="B443" s="8" t="s">
+      <c r="C443" s="9" t="s">
         <v>940</v>
       </c>
-      <c r="C443" s="9" t="s">
-        <v>941</v>
-      </c>
       <c r="D443" s="2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="E443" s="2" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A444" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B444" s="8" t="s">
         <v>377</v>
       </c>
       <c r="C444" s="9" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="E444" s="2" t="s">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="445" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="445" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A445" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B445" s="8" t="s">
         <v>227</v>
       </c>
       <c r="C445" s="9" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="D445" s="2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="E445" s="2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="446" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A446" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="B446" s="8" t="s">
         <v>944</v>
       </c>
-      <c r="B446" s="8" t="s">
+      <c r="C446" s="9" t="s">
         <v>945</v>
       </c>
-      <c r="C446" s="9" t="s">
+      <c r="D446" s="2" t="s">
         <v>946</v>
-      </c>
-      <c r="D446" s="2" t="s">
-        <v>947</v>
       </c>
       <c r="E446" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="447" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A447" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B447" s="8" t="s">
+        <v>947</v>
+      </c>
+      <c r="C447" s="9" t="s">
         <v>948</v>
       </c>
-      <c r="C447" s="9" t="s">
-        <v>949</v>
-      </c>
       <c r="D447" s="2" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="E447" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="448" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A448" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B448" s="8" t="s">
+        <v>949</v>
+      </c>
+      <c r="C448" s="9" t="s">
         <v>950</v>
       </c>
-      <c r="C448" s="9" t="s">
+      <c r="D448" s="2" t="s">
         <v>951</v>
-      </c>
-      <c r="D448" s="2" t="s">
-        <v>952</v>
       </c>
       <c r="E448" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="449" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A449" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B449" s="8" t="s">
         <v>5</v>
       </c>
       <c r="C449" s="9" t="s">
+        <v>952</v>
+      </c>
+      <c r="D449" s="2" t="s">
         <v>953</v>
-      </c>
-      <c r="D449" s="2" t="s">
-        <v>954</v>
       </c>
       <c r="E449" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="450" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A450" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B450" s="8" t="s">
         <v>71</v>
       </c>
       <c r="C450" s="9" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="E450" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="451" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A451" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B451" s="8" t="s">
         <v>560</v>
       </c>
       <c r="C451" s="9" t="s">
+        <v>955</v>
+      </c>
+      <c r="D451" s="2" t="s">
         <v>956</v>
-      </c>
-      <c r="D451" s="2" t="s">
-        <v>957</v>
       </c>
       <c r="E451" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="452" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A452" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B452" s="8" t="s">
         <v>82</v>
       </c>
       <c r="C452" s="9" t="s">
+        <v>957</v>
+      </c>
+      <c r="D452" s="7" t="s">
         <v>958</v>
       </c>
-      <c r="D452" s="7" t="s">
+      <c r="E452" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="453" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A453" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="B453" s="8" t="s">
         <v>959</v>
       </c>
-      <c r="E452" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="453" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A453" s="2" t="s">
-        <v>944</v>
-      </c>
-      <c r="B453" s="8" t="s">
+      <c r="C453" s="9" t="s">
         <v>960</v>
       </c>
-      <c r="C453" s="9" t="s">
+      <c r="D453" s="7" t="s">
         <v>961</v>
       </c>
-      <c r="D453" s="7" t="s">
+      <c r="E453" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="454" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A454" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="B454" s="8" t="s">
         <v>962</v>
       </c>
-      <c r="E453" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="454" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A454" s="2" t="s">
-        <v>944</v>
-      </c>
-      <c r="B454" s="8" t="s">
+      <c r="C454" s="9" t="s">
         <v>963</v>
       </c>
-      <c r="C454" s="9" t="s">
+      <c r="D454" s="7" t="s">
         <v>964</v>
       </c>
-      <c r="D454" s="7" t="s">
+      <c r="E454" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="455" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A455" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="B455" s="8" t="s">
         <v>965</v>
       </c>
-      <c r="E454" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A455" s="2" t="s">
-        <v>944</v>
-      </c>
-      <c r="B455" s="8" t="s">
+      <c r="C455" s="9" t="s">
         <v>966</v>
       </c>
-      <c r="C455" s="9" t="s">
+      <c r="D455" s="7" t="s">
         <v>967</v>
       </c>
-      <c r="D455" s="7" t="s">
+      <c r="E455" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="456" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A456" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="B456" s="8" t="s">
         <v>968</v>
       </c>
-      <c r="E455" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="456" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A456" s="2" t="s">
-        <v>944</v>
-      </c>
-      <c r="B456" s="8" t="s">
+      <c r="C456" s="9" t="s">
         <v>969</v>
       </c>
-      <c r="C456" s="9" t="s">
+      <c r="D456" s="7" t="s">
         <v>970</v>
       </c>
-      <c r="D456" s="7" t="s">
-        <v>971</v>
-      </c>
       <c r="E456" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="457" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A457" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B457" s="8" t="s">
         <v>593</v>
       </c>
       <c r="C457" s="9" t="s">
+        <v>971</v>
+      </c>
+      <c r="D457" s="7" t="s">
         <v>972</v>
       </c>
-      <c r="D457" s="7" t="s">
-        <v>973</v>
-      </c>
       <c r="E457" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="458" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A458" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B458" s="8" t="s">
         <v>377</v>
       </c>
       <c r="C458" s="9" t="s">
+        <v>973</v>
+      </c>
+      <c r="D458" s="7" t="s">
         <v>974</v>
       </c>
-      <c r="D458" s="7" t="s">
-        <v>975</v>
-      </c>
       <c r="E458" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="459" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A459" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B459" s="8" t="s">
         <v>300</v>
       </c>
       <c r="C459" s="9" t="s">
+        <v>975</v>
+      </c>
+      <c r="D459" s="7" t="s">
         <v>976</v>
       </c>
-      <c r="D459" s="7" t="s">
-        <v>977</v>
-      </c>
       <c r="E459" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="460" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A460" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B460" s="2" t="s">
         <v>154</v>
       </c>
       <c r="C460" s="9" t="s">
+        <v>977</v>
+      </c>
+      <c r="D460" s="7" t="s">
         <v>978</v>
-      </c>
-      <c r="D460" s="7" t="s">
-        <v>979</v>
       </c>
       <c r="E460" s="2" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="461" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A461" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B461" s="8" t="s">
+        <v>979</v>
+      </c>
+      <c r="C461" s="9" t="s">
         <v>980</v>
       </c>
-      <c r="C461" s="9" t="s">
+      <c r="D461" s="7" t="s">
         <v>981</v>
       </c>
-      <c r="D461" s="7" t="s">
+      <c r="E461" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="462" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A462" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="B462" s="8" t="s">
         <v>982</v>
       </c>
-      <c r="E461" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="462" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A462" s="2" t="s">
-        <v>944</v>
-      </c>
-      <c r="B462" s="8" t="s">
+      <c r="C462" s="9" t="s">
         <v>983</v>
       </c>
-      <c r="C462" s="9" t="s">
+      <c r="D462" s="7" t="s">
         <v>984</v>
       </c>
-      <c r="D462" s="7" t="s">
+      <c r="E462" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="463" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A463" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="B463" s="8" t="s">
         <v>985</v>
       </c>
-      <c r="E462" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="463" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A463" s="2" t="s">
-        <v>944</v>
-      </c>
-      <c r="B463" s="8" t="s">
+      <c r="C463" s="9" t="s">
         <v>986</v>
       </c>
-      <c r="C463" s="9" t="s">
+      <c r="D463" s="7" t="s">
         <v>987</v>
-      </c>
-      <c r="D463" s="7" t="s">
-        <v>988</v>
       </c>
       <c r="E463" s="2" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="464" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A464" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B464" s="8" t="s">
         <v>317</v>
       </c>
       <c r="C464" s="9" t="s">
+        <v>988</v>
+      </c>
+      <c r="D464" s="7" t="s">
         <v>989</v>
       </c>
-      <c r="D464" s="7" t="s">
+      <c r="E464" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="465" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A465" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="B465" s="8" t="s">
         <v>990</v>
       </c>
-      <c r="E464" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="465" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A465" s="2" t="s">
-        <v>944</v>
-      </c>
-      <c r="B465" s="8" t="s">
+      <c r="C465" s="9" t="s">
         <v>991</v>
       </c>
-      <c r="C465" s="9" t="s">
+      <c r="D465" s="7" t="s">
         <v>992</v>
       </c>
-      <c r="D465" s="7" t="s">
-        <v>993</v>
-      </c>
       <c r="E465" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="466" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A466" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B466" s="8" t="s">
         <v>52</v>
       </c>
       <c r="C466" s="9" t="s">
+        <v>993</v>
+      </c>
+      <c r="D466" s="7" t="s">
         <v>994</v>
       </c>
-      <c r="D466" s="7" t="s">
+      <c r="E466" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="467" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A467" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="B467" s="8" t="s">
+        <v>720</v>
+      </c>
+      <c r="C467" s="9" t="s">
         <v>995</v>
       </c>
-      <c r="E466" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="467" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A467" s="2" t="s">
-        <v>944</v>
-      </c>
-      <c r="B467" s="8" t="s">
-        <v>721</v>
-      </c>
-      <c r="C467" s="9" t="s">
+      <c r="D467" s="7" t="s">
         <v>996</v>
       </c>
-      <c r="D467" s="7" t="s">
+      <c r="E467" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="468" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A468" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="B468" s="8" t="s">
         <v>997</v>
       </c>
-      <c r="E467" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="468" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A468" s="2" t="s">
-        <v>944</v>
-      </c>
-      <c r="B468" s="8" t="s">
+      <c r="C468" s="9" t="s">
         <v>998</v>
       </c>
-      <c r="C468" s="9" t="s">
+      <c r="D468" s="7" t="s">
         <v>999</v>
       </c>
-      <c r="D468" s="7" t="s">
-        <v>1000</v>
-      </c>
       <c r="E468" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="469" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A469" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B469" s="8" t="s">
         <v>131</v>
       </c>
       <c r="C469" s="9" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D469" s="7" t="s">
         <v>1001</v>
       </c>
-      <c r="D469" s="7" t="s">
+      <c r="E469" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="470" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A470" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="B470" s="8" t="s">
         <v>1002</v>
       </c>
-      <c r="E469" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="470" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A470" s="2" t="s">
-        <v>944</v>
-      </c>
-      <c r="B470" s="8" t="s">
+      <c r="C470" s="9" t="s">
         <v>1003</v>
       </c>
-      <c r="C470" s="9" t="s">
+      <c r="D470" s="7" t="s">
         <v>1004</v>
       </c>
-      <c r="D470" s="7" t="s">
+      <c r="E470" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="471" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A471" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="B471" s="8" t="s">
+        <v>772</v>
+      </c>
+      <c r="C471" s="9" t="s">
         <v>1005</v>
       </c>
-      <c r="E470" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="471" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A471" s="2" t="s">
-        <v>944</v>
-      </c>
-      <c r="B471" s="8" t="s">
-        <v>773</v>
-      </c>
-      <c r="C471" s="9" t="s">
-        <v>1006</v>
-      </c>
       <c r="D471" s="7" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="E471" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="472" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A472" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B472" s="8" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C472" s="9" t="s">
         <v>1007</v>
       </c>
-      <c r="C472" s="9" t="s">
-        <v>1008</v>
-      </c>
       <c r="D472" s="2" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="E472" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="473" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A473" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B473" s="8" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="C473" s="9" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="D473" s="2" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E473" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A474" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B474" s="8" t="s">
         <v>131</v>
@@ -12280,117 +12288,117 @@
         <v>26120216</v>
       </c>
       <c r="D474" s="2" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="E474" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="475" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A475" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B475" s="8" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C475" s="9" t="s">
         <v>1010</v>
       </c>
-      <c r="C475" s="9" t="s">
-        <v>1011</v>
-      </c>
       <c r="D475" s="2" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="E475" s="2" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="476" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A476" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B476" s="8" t="s">
         <v>131</v>
       </c>
       <c r="C476" s="9" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="D476" s="2" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E476" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="477" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A477" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B477" s="8" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C477" s="9" t="s">
         <v>1013</v>
       </c>
-      <c r="C477" s="9" t="s">
-        <v>1014</v>
-      </c>
       <c r="D477" s="2" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="E477" s="2" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="478" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A478" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B478" s="8" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C478" s="9" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D478" s="7" t="s">
+        <v>953</v>
+      </c>
+      <c r="E478" s="2" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="479" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A479" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="B479" s="8" t="s">
         <v>1015</v>
       </c>
-      <c r="D478" s="7" t="s">
-        <v>954</v>
-      </c>
-      <c r="E478" s="2" t="s">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="479" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A479" s="2" t="s">
-        <v>944</v>
-      </c>
-      <c r="B479" s="8" t="s">
+      <c r="C479" s="9" t="s">
         <v>1016</v>
       </c>
-      <c r="C479" s="9" t="s">
-        <v>1017</v>
-      </c>
       <c r="D479" s="7" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="E479" s="2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="480" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A480" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B480" s="8" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C480" s="9" t="s">
         <v>1018</v>
       </c>
-      <c r="C480" s="9" t="s">
-        <v>1019</v>
-      </c>
       <c r="D480" s="7" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="E480" s="2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="481" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A481" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B481" s="7" t="s">
         <v>220</v>
@@ -12399,548 +12407,548 @@
         <v>26120122</v>
       </c>
       <c r="D481" s="7" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E481" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="482" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A482" s="2" t="s">
         <v>1020</v>
-      </c>
-      <c r="E481" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="482" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A482" s="2" t="s">
-        <v>1021</v>
       </c>
       <c r="B482" s="8" t="s">
         <v>501</v>
       </c>
       <c r="C482" s="9" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D482" s="2" t="s">
         <v>1022</v>
-      </c>
-      <c r="D482" s="2" t="s">
-        <v>1023</v>
       </c>
       <c r="E482" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="483" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A483" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B483" s="8" t="s">
         <v>501</v>
       </c>
       <c r="C483" s="9" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D483" s="2" t="s">
         <v>1024</v>
-      </c>
-      <c r="D483" s="2" t="s">
-        <v>1025</v>
       </c>
       <c r="E483" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="484" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A484" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B484" s="8" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C484" s="9" t="s">
         <v>1026</v>
       </c>
-      <c r="C484" s="9" t="s">
+      <c r="D484" s="2" t="s">
         <v>1027</v>
       </c>
-      <c r="D484" s="2" t="s">
+      <c r="E484" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="485" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A485" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B485" s="8" t="s">
         <v>1028</v>
       </c>
-      <c r="E484" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="485" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A485" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B485" s="8" t="s">
+      <c r="C485" s="9" t="s">
         <v>1029</v>
       </c>
-      <c r="C485" s="9" t="s">
+      <c r="D485" s="2" t="s">
         <v>1030</v>
-      </c>
-      <c r="D485" s="2" t="s">
-        <v>1031</v>
       </c>
       <c r="E485" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="486" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A486" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B486" s="8" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C486" s="9" t="s">
         <v>1032</v>
       </c>
-      <c r="C486" s="9" t="s">
+      <c r="D486" s="2" t="s">
         <v>1033</v>
-      </c>
-      <c r="D486" s="2" t="s">
-        <v>1034</v>
       </c>
       <c r="E486" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="487" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A487" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B487" s="8" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C487" s="9" t="s">
         <v>1035</v>
       </c>
-      <c r="C487" s="9" t="s">
+      <c r="D487" s="2" t="s">
         <v>1036</v>
-      </c>
-      <c r="D487" s="2" t="s">
-        <v>1037</v>
       </c>
       <c r="E487" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="488" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A488" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B488" s="8" t="s">
         <v>85</v>
       </c>
       <c r="C488" s="9" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="D488" s="2" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="E488" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="489" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A489" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B489" s="8" t="s">
         <v>369</v>
       </c>
       <c r="C489" s="9" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D489" s="2" t="s">
         <v>1039</v>
-      </c>
-      <c r="D489" s="2" t="s">
-        <v>1040</v>
       </c>
       <c r="E489" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="490" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A490" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B490" s="8" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C490" s="9" t="s">
         <v>1041</v>
       </c>
-      <c r="C490" s="9" t="s">
-        <v>1042</v>
-      </c>
       <c r="D490" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="E490" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="491" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A491" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B491" s="8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C491" s="9" t="s">
         <v>1043</v>
       </c>
-      <c r="C491" s="9" t="s">
+      <c r="D491" s="2" t="s">
         <v>1044</v>
-      </c>
-      <c r="D491" s="2" t="s">
-        <v>1045</v>
       </c>
       <c r="E491" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="492" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A492" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B492" s="8" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C492" s="9" t="s">
         <v>1046</v>
       </c>
-      <c r="C492" s="9" t="s">
+      <c r="D492" s="2" t="s">
         <v>1047</v>
-      </c>
-      <c r="D492" s="2" t="s">
-        <v>1048</v>
       </c>
       <c r="E492" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="493" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A493" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B493" s="8" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C493" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="C493" s="9" t="s">
+      <c r="D493" s="2" t="s">
         <v>1050</v>
-      </c>
-      <c r="D493" s="2" t="s">
-        <v>1051</v>
       </c>
       <c r="E493" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="494" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A494" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B494" s="8" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C494" s="9" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D494" s="2" t="s">
         <v>1052</v>
-      </c>
-      <c r="D494" s="2" t="s">
-        <v>1053</v>
       </c>
       <c r="E494" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="495" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A495" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B495" s="8" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C495" s="9" t="s">
         <v>1054</v>
       </c>
-      <c r="C495" s="9" t="s">
-        <v>1055</v>
-      </c>
       <c r="D495" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="E495" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="496" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A496" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B496" s="8" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C496" s="9" t="s">
         <v>1056</v>
       </c>
-      <c r="C496" s="9" t="s">
+      <c r="D496" s="2" t="s">
         <v>1057</v>
       </c>
-      <c r="D496" s="2" t="s">
-        <v>1058</v>
-      </c>
       <c r="E496" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="497" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A497" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B497" s="8" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C497" s="9">
         <v>26130243</v>
       </c>
       <c r="D497" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E497" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="498" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A498" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B498" s="8" t="s">
         <v>1059</v>
       </c>
-      <c r="E497" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="498" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A498" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B498" s="8" t="s">
+      <c r="C498" s="9" t="s">
         <v>1060</v>
       </c>
-      <c r="C498" s="9" t="s">
+      <c r="D498" s="2" t="s">
         <v>1061</v>
       </c>
-      <c r="D498" s="2" t="s">
+      <c r="E498" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="499" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A499" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B499" s="8" t="s">
         <v>1062</v>
       </c>
-      <c r="E498" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="499" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A499" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B499" s="8" t="s">
+      <c r="C499" s="9" t="s">
         <v>1063</v>
       </c>
-      <c r="C499" s="9" t="s">
+      <c r="D499" s="2" t="s">
         <v>1064</v>
       </c>
-      <c r="D499" s="2" t="s">
-        <v>1065</v>
-      </c>
       <c r="E499" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="500" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A500" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B500" s="8" t="s">
         <v>61</v>
       </c>
       <c r="C500" s="9" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D500" s="2" t="s">
         <v>1066</v>
       </c>
-      <c r="D500" s="2" t="s">
-        <v>1067</v>
-      </c>
       <c r="E500" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="501" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A501" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B501" s="8" t="s">
         <v>30</v>
       </c>
       <c r="C501" s="9" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D501" s="2" t="s">
         <v>1068</v>
       </c>
-      <c r="D501" s="2" t="s">
+      <c r="E501" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="502" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A502" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B502" s="8" t="s">
         <v>1069</v>
       </c>
-      <c r="E501" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="502" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A502" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B502" s="8" t="s">
+      <c r="C502" s="9" t="s">
         <v>1070</v>
       </c>
-      <c r="C502" s="9" t="s">
+      <c r="D502" s="2" t="s">
         <v>1071</v>
       </c>
-      <c r="D502" s="2" t="s">
+      <c r="E502" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="503" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A503" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B503" s="8" t="s">
+        <v>738</v>
+      </c>
+      <c r="C503" s="9" t="s">
         <v>1072</v>
       </c>
-      <c r="E502" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="503" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A503" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B503" s="8" t="s">
-        <v>739</v>
-      </c>
-      <c r="C503" s="9" t="s">
+      <c r="D503" s="2" t="s">
         <v>1073</v>
       </c>
-      <c r="D503" s="2" t="s">
-        <v>1074</v>
-      </c>
       <c r="E503" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="504" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A504" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B504" s="8" t="s">
         <v>204</v>
       </c>
       <c r="C504" s="9" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D504" s="2" t="s">
         <v>1075</v>
       </c>
-      <c r="D504" s="2" t="s">
+      <c r="E504" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="505" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A505" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B505" s="8" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C505" s="9" t="s">
         <v>1076</v>
       </c>
-      <c r="E504" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="505" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A505" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B505" s="8" t="s">
-        <v>1056</v>
-      </c>
-      <c r="C505" s="9" t="s">
+      <c r="D505" s="2" t="s">
         <v>1077</v>
       </c>
-      <c r="D505" s="2" t="s">
-        <v>1078</v>
-      </c>
       <c r="E505" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="506" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A506" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B506" s="8" t="s">
         <v>196</v>
       </c>
       <c r="C506" s="9" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D506" s="2" t="s">
         <v>1079</v>
       </c>
-      <c r="D506" s="2" t="s">
-        <v>1080</v>
-      </c>
       <c r="E506" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="507" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A507" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B507" s="8" t="s">
         <v>5</v>
       </c>
       <c r="C507" s="9" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D507" s="2" t="s">
         <v>1081</v>
       </c>
-      <c r="D507" s="2" t="s">
-        <v>1082</v>
-      </c>
       <c r="E507" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="508" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A508" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B508" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C508" s="9" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D508" s="2" t="s">
         <v>1083</v>
       </c>
-      <c r="D508" s="2" t="s">
+      <c r="E508" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="509" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A509" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B509" s="8" t="s">
         <v>1084</v>
       </c>
-      <c r="E508" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="509" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A509" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B509" s="8" t="s">
+      <c r="C509" s="9" t="s">
         <v>1085</v>
       </c>
-      <c r="C509" s="9" t="s">
-        <v>1086</v>
-      </c>
       <c r="D509" s="2" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E509" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="510" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A510" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B510" s="8" t="s">
         <v>37</v>
       </c>
       <c r="C510" s="9" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D510" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="D510" s="2" t="s">
+      <c r="E510" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="511" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A511" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B511" s="8" t="s">
         <v>1088</v>
       </c>
-      <c r="E510" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="511" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A511" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B511" s="8" t="s">
+      <c r="C511" s="9" t="s">
         <v>1089</v>
       </c>
-      <c r="C511" s="9" t="s">
+      <c r="D511" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="D511" s="2" t="s">
+      <c r="E511" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="512" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A512" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B512" s="8" t="s">
+        <v>829</v>
+      </c>
+      <c r="C512" s="9" t="s">
         <v>1091</v>
       </c>
-      <c r="E511" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="512" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A512" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B512" s="8" t="s">
-        <v>830</v>
-      </c>
-      <c r="C512" s="9" t="s">
+      <c r="D512" s="2" t="s">
         <v>1092</v>
       </c>
-      <c r="D512" s="2" t="s">
+      <c r="E512" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="513" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A513" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B513" s="8" t="s">
         <v>1093</v>
       </c>
-      <c r="E512" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="513" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A513" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B513" s="8" t="s">
+      <c r="C513" s="9" t="s">
         <v>1094</v>
-      </c>
-      <c r="C513" s="9" t="s">
-        <v>1095</v>
       </c>
       <c r="D513" s="8">
         <v>18</v>
@@ -12949,389 +12957,389 @@
         <v>33</v>
       </c>
     </row>
-    <row r="514" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A514" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B514" s="8" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C514" s="9" t="s">
         <v>1096</v>
       </c>
-      <c r="C514" s="9" t="s">
+      <c r="D514" s="2" t="s">
         <v>1097</v>
       </c>
-      <c r="D514" s="2" t="s">
-        <v>1098</v>
-      </c>
       <c r="E514" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="515" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A515" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B515" s="8" t="s">
         <v>369</v>
       </c>
       <c r="C515" s="9" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D515" s="2" t="s">
         <v>1099</v>
       </c>
-      <c r="D515" s="2" t="s">
+      <c r="E515" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="516" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A516" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B516" s="8" t="s">
         <v>1100</v>
       </c>
-      <c r="E515" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="516" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A516" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B516" s="8" t="s">
+      <c r="C516" s="9" t="s">
         <v>1101</v>
       </c>
-      <c r="C516" s="9" t="s">
+      <c r="D516" s="2" t="s">
         <v>1102</v>
       </c>
-      <c r="D516" s="2" t="s">
-        <v>1103</v>
-      </c>
       <c r="E516" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="517" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A517" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B517" s="8" t="s">
         <v>377</v>
       </c>
       <c r="C517" s="9" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D517" s="2" t="s">
         <v>1104</v>
       </c>
-      <c r="D517" s="2" t="s">
+      <c r="E517" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="518" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A518" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B518" s="8" t="s">
         <v>1105</v>
       </c>
-      <c r="E517" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="518" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A518" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B518" s="8" t="s">
+      <c r="C518" s="9" t="s">
         <v>1106</v>
       </c>
-      <c r="C518" s="9" t="s">
+      <c r="D518" s="2" t="s">
         <v>1107</v>
       </c>
-      <c r="D518" s="2" t="s">
-        <v>1108</v>
-      </c>
       <c r="E518" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="519" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A519" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B519" s="8" t="s">
         <v>71</v>
       </c>
       <c r="C519" s="9" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D519" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="D519" s="2" t="s">
+      <c r="E519" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="520" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A520" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B520" s="8" t="s">
+        <v>823</v>
+      </c>
+      <c r="C520" s="9" t="s">
         <v>1110</v>
       </c>
-      <c r="E519" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="520" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A520" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B520" s="8" t="s">
-        <v>824</v>
-      </c>
-      <c r="C520" s="9" t="s">
+      <c r="D520" s="2" t="s">
         <v>1111</v>
       </c>
-      <c r="D520" s="2" t="s">
-        <v>1112</v>
-      </c>
       <c r="E520" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="521" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A521" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B521" s="8" t="s">
         <v>34</v>
       </c>
       <c r="C521" s="9" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D521" s="2" t="s">
         <v>1113</v>
       </c>
-      <c r="D521" s="2" t="s">
+      <c r="E521" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="522" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A522" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B522" s="8" t="s">
         <v>1114</v>
       </c>
-      <c r="E521" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="522" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A522" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B522" s="8" t="s">
+      <c r="C522" s="9" t="s">
         <v>1115</v>
       </c>
-      <c r="C522" s="9" t="s">
+      <c r="D522" s="2" t="s">
         <v>1116</v>
       </c>
-      <c r="D522" s="2" t="s">
+      <c r="E522" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="523" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A523" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B523" s="8" t="s">
         <v>1117</v>
       </c>
-      <c r="E522" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="523" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A523" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B523" s="8" t="s">
+      <c r="C523" s="9" t="s">
         <v>1118</v>
       </c>
-      <c r="C523" s="9" t="s">
+      <c r="D523" s="2" t="s">
         <v>1119</v>
       </c>
-      <c r="D523" s="2" t="s">
+      <c r="E523" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="524" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A524" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B524" s="8" t="s">
         <v>1120</v>
       </c>
-      <c r="E523" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="524" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A524" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B524" s="8" t="s">
+      <c r="C524" s="9" t="s">
         <v>1121</v>
       </c>
-      <c r="C524" s="9" t="s">
+      <c r="D524" s="2" t="s">
         <v>1122</v>
       </c>
-      <c r="D524" s="2" t="s">
+      <c r="E524" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="525" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A525" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B525" s="8" t="s">
         <v>1123</v>
       </c>
-      <c r="E524" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="525" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A525" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B525" s="8" t="s">
+      <c r="C525" s="9" t="s">
         <v>1124</v>
       </c>
-      <c r="C525" s="9" t="s">
+      <c r="D525" s="2" t="s">
         <v>1125</v>
       </c>
-      <c r="D525" s="2" t="s">
+      <c r="E525" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="526" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A526" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B526" s="8" t="s">
         <v>1126</v>
       </c>
-      <c r="E525" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="526" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A526" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B526" s="8" t="s">
+      <c r="C526" s="9" t="s">
         <v>1127</v>
       </c>
-      <c r="C526" s="9" t="s">
+      <c r="D526" s="2" t="s">
         <v>1128</v>
       </c>
-      <c r="D526" s="2" t="s">
-        <v>1129</v>
-      </c>
       <c r="E526" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="527" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A527" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B527" s="8" t="s">
         <v>596</v>
       </c>
       <c r="C527" s="9" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D527" s="2" t="s">
         <v>1130</v>
       </c>
-      <c r="D527" s="2" t="s">
-        <v>1131</v>
-      </c>
       <c r="E527" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="528" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A528" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B528" s="8" t="s">
         <v>99</v>
       </c>
       <c r="C528" s="9" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D528" s="2" t="s">
         <v>1132</v>
       </c>
-      <c r="D528" s="2" t="s">
+      <c r="E528" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="529" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A529" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B529" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="E528" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="529" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A529" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B529" s="8" t="s">
+      <c r="C529" s="9" t="s">
         <v>1134</v>
       </c>
-      <c r="C529" s="9" t="s">
+      <c r="D529" s="2" t="s">
         <v>1135</v>
       </c>
-      <c r="D529" s="2" t="s">
-        <v>1136</v>
-      </c>
       <c r="E529" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="530" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A530" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B530" s="8" t="s">
         <v>260</v>
       </c>
       <c r="C530" s="9" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D530" s="2" t="s">
         <v>1137</v>
       </c>
-      <c r="D530" s="2" t="s">
+      <c r="E530" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="531" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A531" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B531" s="8" t="s">
         <v>1138</v>
       </c>
-      <c r="E530" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="531" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A531" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B531" s="8" t="s">
+      <c r="C531" s="9" t="s">
         <v>1139</v>
       </c>
-      <c r="C531" s="9" t="s">
+      <c r="D531" s="2" t="s">
         <v>1140</v>
       </c>
-      <c r="D531" s="2" t="s">
-        <v>1141</v>
-      </c>
       <c r="E531" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="532" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A532" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B532" s="8" t="s">
         <v>403</v>
       </c>
       <c r="C532" s="9" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D532" s="2" t="s">
         <v>1142</v>
       </c>
-      <c r="D532" s="2" t="s">
-        <v>1143</v>
-      </c>
       <c r="E532" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="533" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A533" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B533" s="8" t="s">
         <v>213</v>
       </c>
       <c r="C533" s="9" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D533" s="2" t="s">
         <v>1144</v>
       </c>
-      <c r="D533" s="2" t="s">
+      <c r="E533" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="534" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A534" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B534" s="8" t="s">
         <v>1145</v>
       </c>
-      <c r="E533" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="534" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A534" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B534" s="8" t="s">
+      <c r="C534" s="9" t="s">
         <v>1146</v>
       </c>
-      <c r="C534" s="9" t="s">
+      <c r="D534" s="2" t="s">
         <v>1147</v>
       </c>
-      <c r="D534" s="2" t="s">
-        <v>1148</v>
-      </c>
       <c r="E534" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="535" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A535" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B535" s="8" t="s">
         <v>196</v>
       </c>
       <c r="C535" s="9" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D535" s="2" t="s">
         <v>1149</v>
       </c>
-      <c r="D535" s="2" t="s">
+      <c r="E535" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="536" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A536" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B536" s="8" t="s">
         <v>1150</v>
       </c>
-      <c r="E535" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="536" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A536" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B536" s="8" t="s">
+      <c r="C536" s="9" t="s">
         <v>1151</v>
-      </c>
-      <c r="C536" s="9" t="s">
-        <v>1152</v>
       </c>
       <c r="D536" s="2" t="s">
         <v>323</v>
@@ -13340,377 +13348,377 @@
         <v>33</v>
       </c>
     </row>
-    <row r="537" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A537" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B537" s="8" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C537" s="9" t="s">
         <v>1153</v>
       </c>
-      <c r="C537" s="9" t="s">
+      <c r="D537" s="2" t="s">
         <v>1154</v>
       </c>
-      <c r="D537" s="2" t="s">
+      <c r="E537" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="538" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A538" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B538" s="8" t="s">
         <v>1155</v>
       </c>
-      <c r="E537" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="538" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A538" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B538" s="8" t="s">
+      <c r="C538" s="9" t="s">
         <v>1156</v>
       </c>
-      <c r="C538" s="9" t="s">
+      <c r="D538" s="2" t="s">
         <v>1157</v>
       </c>
-      <c r="D538" s="2" t="s">
-        <v>1158</v>
-      </c>
       <c r="E538" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="539" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A539" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B539" s="8" t="s">
         <v>131</v>
       </c>
       <c r="C539" s="9" t="s">
+        <v>1158</v>
+      </c>
+      <c r="D539" s="2" t="s">
         <v>1159</v>
       </c>
-      <c r="D539" s="2" t="s">
+      <c r="E539" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="540" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A540" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B540" s="8" t="s">
         <v>1160</v>
       </c>
-      <c r="E539" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="540" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A540" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B540" s="8" t="s">
+      <c r="C540" s="9" t="s">
         <v>1161</v>
       </c>
-      <c r="C540" s="9" t="s">
+      <c r="D540" s="2" t="s">
         <v>1162</v>
       </c>
-      <c r="D540" s="2" t="s">
-        <v>1163</v>
-      </c>
       <c r="E540" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="541" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A541" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B541" s="8" t="s">
         <v>213</v>
       </c>
       <c r="C541" s="9" t="s">
+        <v>1163</v>
+      </c>
+      <c r="D541" s="2" t="s">
         <v>1164</v>
       </c>
-      <c r="D541" s="2" t="s">
+      <c r="E541" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="542" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A542" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B542" s="8" t="s">
         <v>1165</v>
-      </c>
-      <c r="E541" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="542" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A542" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B542" s="8" t="s">
-        <v>1166</v>
       </c>
       <c r="C542" s="9">
         <v>26130236</v>
       </c>
       <c r="D542" s="2" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="E542" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="543" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A543" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B543" s="8" t="s">
         <v>193</v>
       </c>
       <c r="C543" s="9" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D543" s="2" t="s">
         <v>1167</v>
       </c>
-      <c r="D543" s="2" t="s">
-        <v>1168</v>
-      </c>
       <c r="E543" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="544" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A544" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B544" s="2" t="s">
         <v>129</v>
       </c>
       <c r="C544" s="9" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D544" s="2" t="s">
         <v>1169</v>
       </c>
-      <c r="D544" s="2" t="s">
+      <c r="E544" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="545" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A545" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B545" s="8" t="s">
         <v>1170</v>
       </c>
-      <c r="E544" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="545" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A545" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B545" s="8" t="s">
+      <c r="C545" s="9" t="s">
         <v>1171</v>
       </c>
-      <c r="C545" s="9" t="s">
-        <v>1172</v>
-      </c>
       <c r="D545" s="2" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="E545" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="546" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A546" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B546" s="8" t="s">
         <v>196</v>
       </c>
       <c r="C546" s="9" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="D546" s="2" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="E546" s="2" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="547" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A547" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B547" s="8" t="s">
         <v>512</v>
       </c>
       <c r="C547" s="9" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="D547" s="2" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="E547" s="2" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="548" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A548" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B548" s="8" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="C548" s="9" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="D548" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="E548" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="549" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A549" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B549" s="8" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C549" s="9" t="s">
         <v>1176</v>
       </c>
-      <c r="C549" s="9" t="s">
+      <c r="D549" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E549" s="2" t="s">
         <v>1177</v>
       </c>
-      <c r="D549" s="2" t="s">
-        <v>1025</v>
-      </c>
-      <c r="E549" s="2" t="s">
+    </row>
+    <row r="550" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A550" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B550" s="8" t="s">
         <v>1178</v>
       </c>
-    </row>
-    <row r="550" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A550" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B550" s="8" t="s">
+      <c r="C550" s="9" t="s">
         <v>1179</v>
       </c>
-      <c r="C550" s="9" t="s">
-        <v>1180</v>
-      </c>
       <c r="D550" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="E550" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="551" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A551" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B551" s="8" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C551" s="9" t="s">
         <v>1181</v>
       </c>
-      <c r="C551" s="9" t="s">
+      <c r="D551" s="2" t="s">
         <v>1182</v>
       </c>
-      <c r="D551" s="2" t="s">
+      <c r="E551" s="2" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="552" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A552" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B552" s="8" t="s">
         <v>1183</v>
-      </c>
-      <c r="E551" s="2" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="552" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A552" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B552" s="8" t="s">
-        <v>1184</v>
       </c>
       <c r="C552" s="9"/>
       <c r="D552" s="2" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E552" s="2" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="553" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A553" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B553" s="8" t="s">
         <v>1185</v>
       </c>
-    </row>
-    <row r="553" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A553" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B553" s="8" t="s">
+      <c r="C553" s="9" t="s">
         <v>1186</v>
       </c>
-      <c r="C553" s="9" t="s">
+      <c r="D553" s="2" t="s">
         <v>1187</v>
-      </c>
-      <c r="D553" s="2" t="s">
-        <v>1188</v>
       </c>
       <c r="E553" s="2" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="554" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A554" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B554" s="8" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="C554" s="9" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="D554" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="E554" s="2" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="555" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A555" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B555" s="8" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="C555" s="9" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D555" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E555" s="2" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="556" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A556" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B556" s="8" t="s">
         <v>1190</v>
       </c>
-      <c r="D555" s="2" t="s">
-        <v>1023</v>
-      </c>
-      <c r="E555" s="2" t="s">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="556" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A556" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B556" s="8" t="s">
+      <c r="C556" s="9" t="s">
         <v>1191</v>
       </c>
-      <c r="C556" s="9" t="s">
-        <v>1192</v>
-      </c>
       <c r="D556" s="2" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="E556" s="2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="557" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A557" s="17" t="s">
         <v>599</v>
       </c>
       <c r="B557" s="17" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C557" s="24" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D557" s="17" t="s">
         <v>1193</v>
       </c>
-      <c r="D557" s="17" t="s">
+      <c r="E557" s="25" t="s">
         <v>1194</v>
       </c>
-      <c r="E557" s="25" t="s">
-        <v>1195</v>
-      </c>
-    </row>
-    <row r="558" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="558" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A558" s="17" t="s">
         <v>599</v>
       </c>
       <c r="B558" s="17" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C558" s="24" t="s">
         <v>1196</v>
-      </c>
-      <c r="C558" s="24" t="s">
-        <v>1197</v>
       </c>
       <c r="D558" s="17"/>
       <c r="E558" s="25" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="559" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A559" s="17" t="s">
         <v>599</v>
       </c>
@@ -13718,15 +13726,16 @@
         <v>129</v>
       </c>
       <c r="C559" s="24" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D559" s="17"/>
       <c r="E559" s="25" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1" xr:uid="{D186CE86-78E5-400A-95E9-7078AC52DD14}"/>
+  <autoFilter ref="A1:E559" xr:uid="{D186CE86-78E5-400A-95E9-7078AC52DD14}"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="D134">
     <cfRule type="cellIs" dxfId="5" priority="6" stopIfTrue="1" operator="equal">
       <formula>"cerrar"</formula>
@@ -13758,5 +13767,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>